--- a/Wikidata Delta/qa_gen_excels/pep_qatar_living_relevant_cleaned.xlsx
+++ b/Wikidata Delta/qa_gen_excels/pep_qatar_living_relevant_cleaned.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR115"/>
+  <dimension ref="A1:AR116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -667,7 +667,11 @@
           <t>Male</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Qatari Politician</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
         <v>0</v>
@@ -711,7 +715,7 @@
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="V2" t="n">
@@ -737,7 +741,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Qatar']</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -787,7 +791,7 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Politician']</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -833,7 +837,11 @@
           <t>Female</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Qatari Academic And Politician</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
         <v>0</v>
@@ -877,7 +885,7 @@
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="V3" t="n">
@@ -903,17 +911,17 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Qatar']</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>['Also Known As', 'Original Script Name', 'Also Known As']</t>
+          <t>['Also Known As', 'Also Known As', 'Also Known As', 'Also Known As', 'Also Known As', 'Also Known As']</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>['Hind Al Muftah', 'هند المفتاح', 'Hind Abdul Rahman Al Muftah']</t>
+          <t>['Hend Abdulrahman Al Muftah', 'Hind Abdul Rahman Al Muftah', 'Hend Al Muftah', 'Hind Bint Abd Ar Rahman Al Muftah', 'Hend Abdurrahman Mohamed Mubarak Al Muftah', 'Hind Al Muftah']</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -953,7 +961,7 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Politician']</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -999,7 +1007,11 @@
           <t>Female</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Qatari Academic And Politician</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
         <v>0</v>
@@ -1043,7 +1055,7 @@
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="V4" t="n">
@@ -1069,17 +1081,17 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Qatar']</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>['Also Known As', 'Original Script Name']</t>
+          <t>['Also Known As', 'Also Known As', 'Also Known As', 'Also Known As', 'Also Known As']</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>['Aisha Yousef Al Mannai', 'عائشة المناعي']</t>
+          <t>['Aisha Yusuf Omar Al Mannai', 'Aisha Youssuf Omar Al Hamad Al Mannai', 'Aisha Bint Yousuf Al Mannai', 'Aisha Yousef Al Mannai', 'Aisha Al Mannai']</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1119,7 +1131,7 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Academic', 'Politician']</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -1165,7 +1177,11 @@
           <t>Female</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Qatari Civil Servant And Politician</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
         <v>0</v>
@@ -1213,7 +1229,7 @@
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="V5" t="n">
@@ -1239,17 +1255,17 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Qatar']</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Also Known As']</t>
+          <t>['Also Known As', 'Also Known As', 'Also Known As']</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>['ريم المنصوري', 'Reem Al Mansoori']</t>
+          <t>['Reem Mohamed Rashid Al Hammoudi Al Mansouri', 'Reem Bint Mohammed Al Mansoori', 'Reem Al Mansoori']</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -1289,7 +1305,7 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Politician']</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -1383,7 +1399,7 @@
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="V6" t="n">
@@ -1459,7 +1475,7 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Diplomat', 'Politician']</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -1553,7 +1569,7 @@
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="V7" t="n">
@@ -1629,7 +1645,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Diplomat', 'Politician']</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -1675,7 +1691,11 @@
           <t>Male</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Qatari Politician</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
         <v>0</v>
@@ -1719,7 +1739,7 @@
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="V8" t="n">
@@ -1745,7 +1765,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Qatar']</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
@@ -1795,7 +1815,7 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Diplomat', 'Politician']</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -1889,7 +1909,7 @@
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="V9" t="n">
@@ -1965,7 +1985,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Diplomat', 'Politician']</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -2011,7 +2031,11 @@
           <t>Male</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Qatari Diplomat</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="n">
         <v>0</v>
@@ -2055,7 +2079,7 @@
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="V10" t="n">
@@ -2081,7 +2105,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Qatar']</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
@@ -2131,7 +2155,7 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Diplomat', 'Politician']</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
@@ -2177,7 +2201,11 @@
           <t>Male</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Qatari Politician</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="n">
         <v>0</v>
@@ -2221,7 +2249,7 @@
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="V11" t="n">
@@ -2247,7 +2275,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Qatar']</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
@@ -2297,7 +2325,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Diplomat', 'Politician']</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
@@ -2343,7 +2371,11 @@
           <t>Male</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Qatari Politician</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="n">
         <v>0</v>
@@ -2391,7 +2423,7 @@
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="V12" t="n">
@@ -2417,17 +2449,17 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Qatar']</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As']</t>
+          <t>['Also Known As', 'Also Known As']</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>['علی بن احمد الکواری', 'علي أحمد الكواري', 'আলী বিন আহমেদ আল কুওয়ারি', 'Ali Bin Ahmed Al Kuwari']</t>
+          <t>['Ali Ahmed Al Kuwari', 'Ali Bin Ahmed Al Kuwari']</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -2467,22 +2499,22 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Civil Servant', 'Politician']</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Minister Of Commerce And Industry', 'Minister Of Finance Of Qatar']</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['2018-11-01', '2021-10-19']</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['2021-10-19', None]</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
@@ -2565,7 +2597,7 @@
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="V13" t="n">
@@ -2641,7 +2673,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Diplomat', 'Politician']</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
@@ -2735,7 +2767,7 @@
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="V14" t="n">
@@ -2811,7 +2843,7 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Diplomat', 'Politician']</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
@@ -2905,7 +2937,7 @@
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="V15" t="n">
@@ -2981,7 +3013,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Diplomat', 'Politician']</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
@@ -3079,7 +3111,7 @@
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="V16" t="n">
@@ -3155,7 +3187,7 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Diplomat', 'Politician']</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
@@ -3253,7 +3285,7 @@
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="V17" t="n">
@@ -3284,12 +3316,12 @@
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name']</t>
+          <t>['Original Script Name', 'Also Known As', 'Original Script Name']</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>['مانع بن عبد الہادی ہاجری', 'مانع عبد الهادي الهاجري', 'Man A Abdul Hadi Al Hajri', 'مانع بن عبد الهادي الهاجري', 'مانع بن عبد الهادي مانع الشهواني الهاجري']</t>
+          <t>['مانع بن عبد الهادي مانع الشهواني الهاجري', 'Man A Abdul Hadi Al Hajri', 'مانع بن عبد الهادي الهاجري']</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -3366,7 +3398,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ali Bin Abdullah Zaid Al Mahmoud</t>
+          <t>Ali Bin Abdullah Zaid Al Mahmud</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -3431,7 +3463,7 @@
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="V18" t="n">
@@ -3462,12 +3494,12 @@
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Original Script Name']</t>
+          <t>['Original Script Name']</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>['علي بن عبد الله زيد آل محمود', 'Алі бін Абдулла Заїд Аль Махмуд']</t>
+          <t>["['Алі бін Абдулла Заїд Аль Махмуд']"]</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -3507,7 +3539,7 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Diplomat', 'Politician']</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
@@ -3601,7 +3633,7 @@
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="V19" t="n">
@@ -3677,7 +3709,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Diplomat', 'Politician']</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
@@ -3775,7 +3807,7 @@
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="V20" t="n">
@@ -3851,7 +3883,7 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Diplomat', 'Politician']</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
@@ -3897,7 +3929,11 @@
           <t>Male</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Qatari Politician</t>
+        </is>
+      </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
         <v>0</v>
@@ -3941,7 +3977,7 @@
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="V21" t="n">
@@ -3967,7 +4003,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Qatar']</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
@@ -4017,7 +4053,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Diplomat', 'Politician']</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
@@ -4063,7 +4099,11 @@
           <t>Female</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Qatari Businesswoman</t>
+        </is>
+      </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
         <v>0</v>
@@ -4107,7 +4147,7 @@
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="V22" t="n">
@@ -4133,17 +4173,17 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Qatar']</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>['Also Known As']</t>
+          <t>['Also Known As', 'Also Known As', 'Also Known As', 'Also Known As']</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>['Hanadi Bint Nasser Al Thani']</t>
+          <t>['Sheikha Hanadi Bint Nasser Al Thani', 'Hanadi Al Thani', 'Sheikha Hanadi Al Thani', 'Hanadi Bint Nasser Al Thani']</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -4183,7 +4223,7 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Businessperson']</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
@@ -4229,7 +4269,11 @@
           <t>Female</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Qatari Businesswoman</t>
+        </is>
+      </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
         <v>0</v>
@@ -4273,7 +4317,7 @@
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="V23" t="n">
@@ -4299,7 +4343,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Qatar']</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
@@ -4349,7 +4393,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Businessperson']</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
@@ -4395,7 +4439,11 @@
           <t>Female</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Qatari Businesswoman</t>
+        </is>
+      </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
         <v>0</v>
@@ -4439,7 +4487,7 @@
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="V24" t="n">
@@ -4465,7 +4513,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Qatar']</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
@@ -4515,7 +4563,7 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Businessperson']</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
@@ -4561,7 +4609,11 @@
           <t>Female</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>President Of The Womens Sports Committee In Qatar</t>
+        </is>
+      </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
         <v>0</v>
@@ -4605,7 +4657,7 @@
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="V25" t="n">
@@ -4631,17 +4683,17 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Qatar']</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>['Also Known As']</t>
+          <t>['Also Known As', 'Also Known As', 'Also Known As']</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>['Ahlam Salem Al Mana']</t>
+          <t>['Ahlam Salem Al Mana', 'Ahlam Al Mana', 'Ahlam Salem Mubarak Al Mana']</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
@@ -4681,7 +4733,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Politician', 'Sports Executive']</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
@@ -4727,7 +4779,11 @@
           <t>Male</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Politician In Qatar</t>
+        </is>
+      </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
         <v>0</v>
@@ -4771,7 +4827,7 @@
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="V26" t="n">
@@ -4797,17 +4853,17 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Qatar']</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>['Also Known As', 'Original Script Name', 'Also Known As']</t>
+          <t>['Original Script Name', 'Also Known As']</t>
         </is>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>['Ghnaem Bin Shaheen Bin Ghanem Al Ghanim', 'غانم الغانم', 'Ghanem Bin Shaheen Bin Ghanem Al Ghanim']</t>
+          <t>['غانم بن شاهين بن غانم الغانم', 'Ghanem Bin Shaheen Bin Ghanem Al Ghanim']</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
@@ -4847,22 +4903,22 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Military Personnel', 'Politician']</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Minister Of Awqaf And Islamic Affairs']</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['2021-10-19']</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[None]</t>
         </is>
       </c>
       <c r="AQ26" t="inlineStr">
@@ -4893,7 +4949,11 @@
           <t>Female</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Politician In Qatar</t>
+        </is>
+      </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="n">
         <v>0</v>
@@ -4941,7 +5001,7 @@
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="V27" t="n">
@@ -4967,17 +5027,17 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Qatar']</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Original Script Name', 'Also Known As', 'Also Known As']</t>
+          <t>['Also Known As']</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>['مريم المسند', 'مریم بنت علی بن ناصر المسند', 'Mariam Bint Ali Bin Nasser Al Misnad', 'Mariam Bint Ali Ben Nasser Al Misnad']</t>
+          <t>['Mariam Bint Ali Ben Nasser Al Misnad']</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
@@ -5017,22 +5077,22 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Politician']</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Minister Of Social Development And Family']</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['2021-10-19']</t>
         </is>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[None]</t>
         </is>
       </c>
       <c r="AQ27" t="inlineStr">
@@ -5063,7 +5123,11 @@
           <t>Female</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Qatari Businesswoman, Ceo Of Qnb Capital</t>
+        </is>
+      </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="n">
         <v>0</v>
@@ -5107,7 +5171,7 @@
       <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="V28" t="n">
@@ -5133,7 +5197,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Qatar']</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
@@ -5183,7 +5247,7 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Businessperson']</t>
         </is>
       </c>
       <c r="AN28" t="inlineStr">
@@ -5229,7 +5293,11 @@
           <t>Female</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Qatari Politician, Deputy Speaker Of The Shura Council</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="n">
         <v>0</v>
@@ -5277,7 +5345,7 @@
       <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="V29" t="n">
@@ -5303,17 +5371,17 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Qatar']</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Also Known As']</t>
+          <t>['Also Known As', 'Also Known As', 'Also Known As', 'Also Known As']</t>
         </is>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>['حمدة السليطي', 'Hamda Bint Hassan Al Sulaiti']</t>
+          <t>['Hamda Hassan Al Sulaiti', 'Hamada Hasan Al Sulaiti', 'Hamda Bint Hassan Al Sulaiti', 'Hamda Hasan Al Sulaiti']</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
@@ -5353,7 +5421,7 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Politician']</t>
         </is>
       </c>
       <c r="AN29" t="inlineStr">
@@ -5399,7 +5467,11 @@
           <t>Female</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Qatari Judge, First Woman To Work As A Criminal Judge In Qatar</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="n">
         <v>0</v>
@@ -5443,7 +5515,7 @@
       <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="V30" t="n">
@@ -5469,17 +5541,17 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Qatar']</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Also Known As']</t>
+          <t>['Also Known As', 'Also Known As', 'Also Known As']</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>['فاطمة عبد الله المال', 'Fatima Abdullah Al Mal']</t>
+          <t>['Fatima Abdulla Al Mal', 'Fatima Bint Abdullah Al Mall', 'Fatima Abdullah Al Mal']</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
@@ -5519,7 +5591,7 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Judge']</t>
         </is>
       </c>
       <c r="AN30" t="inlineStr">
@@ -5565,7 +5637,11 @@
           <t>Female</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Qatari Judge</t>
+        </is>
+      </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
         <v>0</v>
@@ -5609,7 +5685,7 @@
       <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="V31" t="n">
@@ -5635,17 +5711,17 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Qatar']</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>['Also Known As']</t>
+          <t>['Also Known As', 'Also Known As']</t>
         </is>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>['Aisha Hassan Al Emadi']</t>
+          <t>['Aisha Hassan Al Emadi', 'Aisha Bint Hassan Al Emadi']</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
@@ -5685,7 +5761,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Judge']</t>
         </is>
       </c>
       <c r="AN31" t="inlineStr">
@@ -5731,7 +5807,11 @@
           <t>Female</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Qatari Businesswoman</t>
+        </is>
+      </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
         <v>0</v>
@@ -5775,7 +5855,7 @@
       <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="V32" t="n">
@@ -5801,7 +5881,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Qatar']</t>
         </is>
       </c>
       <c r="AD32" t="inlineStr">
@@ -5851,7 +5931,7 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Businessperson']</t>
         </is>
       </c>
       <c r="AN32" t="inlineStr">
@@ -5897,7 +5977,11 @@
           <t>Female</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Qatari Businessperson</t>
+        </is>
+      </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
         <v>0</v>
@@ -5941,7 +6025,7 @@
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="V33" t="n">
@@ -5967,17 +6051,17 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Qatar']</t>
         </is>
       </c>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>['Also Known As']</t>
+          <t>['Also Known As', 'Also Known As']</t>
         </is>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>['Amal Dahawi Al Shammri']</t>
+          <t>['Amal Al Shammri', 'Amal Dahawi Al Shammri']</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
@@ -6017,7 +6101,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Businessperson']</t>
         </is>
       </c>
       <c r="AN33" t="inlineStr">
@@ -6063,7 +6147,11 @@
           <t>Female</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Ceo Of Doha Film Institute</t>
+        </is>
+      </c>
       <c r="F34" t="inlineStr">
         <is>
           <t>Doha</t>
@@ -6111,7 +6199,7 @@
       <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="V34" t="n">
@@ -6137,17 +6225,17 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Qatar']</t>
         </is>
       </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Also Known As']</t>
+          <t>['Also Known As']</t>
         </is>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>['ফাতমা আল রিমাইহি', 'Fatma Al Remaihi']</t>
+          <t>['Fatma Al Remaihi']</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
@@ -6187,7 +6275,7 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Businessperson', 'Chief Executive Officer']</t>
         </is>
       </c>
       <c r="AN34" t="inlineStr">
@@ -6281,7 +6369,7 @@
       <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="V35" t="n">
@@ -6357,7 +6445,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Businessperson']</t>
         </is>
       </c>
       <c r="AN35" t="inlineStr">
@@ -6403,7 +6491,11 @@
           <t>Female</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Qatari Businesswoman</t>
+        </is>
+      </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
         <v>0</v>
@@ -6451,7 +6543,7 @@
       <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="V36" t="n">
@@ -6477,17 +6569,17 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Qatar']</t>
         </is>
       </c>
       <c r="AD36" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Also Known As']</t>
+          <t>['Also Known As', 'Also Known As', 'Also Known As', 'Also Known As']</t>
         </is>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>['Алануд бінт Хамад Аль Тані', 'Alanoud Bint Hamad Al Thani', 'अलानौद बिन्त हमद अल थानी', 'العنود بنت حمد آل ثاني', 'Alanoud Al Thani']</t>
+          <t>['Alanoud Hamad Thani', 'Alanoud Bint Hamad Al Thani', 'Sheikha Alanoud Bint Hamad Al Thani', 'Alanoud Al Thani']</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
@@ -6527,7 +6619,7 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Banker', 'Business Executive', 'Businessperson', 'Manager']</t>
         </is>
       </c>
       <c r="AN36" t="inlineStr">
@@ -6573,7 +6665,11 @@
           <t>Female</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Qatari Politician, Minister Of Education</t>
+        </is>
+      </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
         <v>0</v>
@@ -6617,7 +6713,7 @@
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="V37" t="n">
@@ -6643,7 +6739,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Qatar']</t>
         </is>
       </c>
       <c r="AD37" t="inlineStr">
@@ -6693,7 +6789,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Politician']</t>
         </is>
       </c>
       <c r="AN37" t="inlineStr">
@@ -6739,7 +6835,11 @@
           <t>Female</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Qatari Politician</t>
+        </is>
+      </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
         <v>0</v>
@@ -6783,7 +6883,7 @@
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="V38" t="n">
@@ -6809,7 +6909,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Qatar']</t>
         </is>
       </c>
       <c r="AD38" t="inlineStr">
@@ -6859,7 +6959,7 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Politician']</t>
         </is>
       </c>
       <c r="AN38" t="inlineStr">
@@ -6905,7 +7005,11 @@
           <t>Female</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Qatari Politician</t>
+        </is>
+      </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
         <v>0</v>
@@ -6949,7 +7053,7 @@
       <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="V39" t="n">
@@ -6975,7 +7079,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Qatar']</t>
         </is>
       </c>
       <c r="AD39" t="inlineStr">
@@ -7025,7 +7129,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Politician']</t>
         </is>
       </c>
       <c r="AN39" t="inlineStr">
@@ -7071,7 +7175,11 @@
           <t>Female</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Qatari Clothes Designer And Businessperson</t>
+        </is>
+      </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
         <v>0</v>
@@ -7115,7 +7223,7 @@
       <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="V40" t="n">
@@ -7141,7 +7249,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Qatar']</t>
         </is>
       </c>
       <c r="AD40" t="inlineStr">
@@ -7191,7 +7299,7 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Businessperson', 'Fashion Designer']</t>
         </is>
       </c>
       <c r="AN40" t="inlineStr">
@@ -7237,7 +7345,11 @@
           <t>Female</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Qatari Businessperson</t>
+        </is>
+      </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="n">
         <v>0</v>
@@ -7281,7 +7393,7 @@
       <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="V41" t="n">
@@ -7307,7 +7419,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Qatar']</t>
         </is>
       </c>
       <c r="AD41" t="inlineStr">
@@ -7357,7 +7469,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Businessperson']</t>
         </is>
       </c>
       <c r="AN41" t="inlineStr">
@@ -7403,7 +7515,11 @@
           <t>Female</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Qatari Businessperson</t>
+        </is>
+      </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="n">
         <v>0</v>
@@ -7447,7 +7563,7 @@
       <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="V42" t="n">
@@ -7473,7 +7589,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Qatar']</t>
         </is>
       </c>
       <c r="AD42" t="inlineStr">
@@ -7523,7 +7639,7 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Businessperson']</t>
         </is>
       </c>
       <c r="AN42" t="inlineStr">
@@ -7569,7 +7685,11 @@
           <t>Female</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Qatari Businessperson</t>
+        </is>
+      </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="n">
         <v>0</v>
@@ -7613,7 +7733,7 @@
       <c r="T43" t="inlineStr"/>
       <c r="U43" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="V43" t="n">
@@ -7639,7 +7759,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Qatar']</t>
         </is>
       </c>
       <c r="AD43" t="inlineStr">
@@ -7689,7 +7809,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Businessperson']</t>
         </is>
       </c>
       <c r="AN43" t="inlineStr">
@@ -7735,7 +7855,11 @@
           <t>Female</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Qatari Businessperson</t>
+        </is>
+      </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="n">
         <v>0</v>
@@ -7779,7 +7903,7 @@
       <c r="T44" t="inlineStr"/>
       <c r="U44" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="V44" t="n">
@@ -7805,7 +7929,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Qatar']</t>
         </is>
       </c>
       <c r="AD44" t="inlineStr">
@@ -7855,7 +7979,7 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Businessperson']</t>
         </is>
       </c>
       <c r="AN44" t="inlineStr">
@@ -7892,7 +8016,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Mubarak Bin Ali Al Khatir</t>
+          <t>Hamad Bin Abdulaziz Al Kawari</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
@@ -7903,10 +8027,14 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Qatari Politician</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr"/>
+          <t>Qatari Diplomat</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Al Ghariyah</t>
+        </is>
+      </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
@@ -7917,7 +8045,7 @@
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>{"Reference ID": "Q12238502"}</t>
+          <t>{"Educated At": "Cairo University, Paris-Sorbonne University - Paris IV, Saint Joseph University of Beirut", "Reference ID": "Q12208756"}</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -7940,7 +8068,11 @@
           <t>Individual</t>
         </is>
       </c>
-      <c r="R45" t="inlineStr"/>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>https://upload.wikimedia.org/wikipedia/commons/b/b0/Hamad_Bin_Abdulaziz_Al-Kawari.jpg</t>
+        </is>
+      </c>
       <c r="S45" t="inlineStr">
         <is>
           <t>qa_gen</t>
@@ -7949,7 +8081,7 @@
       <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="V45" t="n">
@@ -7970,7 +8102,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>['2000-01-01']</t>
+          <t>['1948-01-01']</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
@@ -7980,12 +8112,12 @@
       </c>
       <c r="AD45" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Original Script Name', 'Also Known As']</t>
+          <t>['Also Known As', 'Original Script Name', 'Also Known As']</t>
         </is>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
-          <t>['مبارك بن علي الخاطر', 'مبارك بن علي آل خاطر', 'Mubarak Bin Ali Al Khatir']</t>
+          <t>['Hamad Bin Abdulaziz Al Kawari', 'حمد بن عبدالعزيز الكواري', 'Hamad Bin Abdulaziz Al Kuwari']</t>
         </is>
       </c>
       <c r="AF45" t="inlineStr">
@@ -8025,12 +8157,12 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Author', 'Diplomat', 'Politician']</t>
         </is>
       </c>
       <c r="AN45" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Minister Of Culture']</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
@@ -8062,7 +8194,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Masoud Bin Mohammed Al Ameri</t>
+          <t>Mubarak Bin Ali Al Khatir</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
@@ -8087,7 +8219,7 @@
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>{"Educated At": "Cairo University, Faculty of medicine Cairo university", "Reference ID": "Q12242945"}</t>
+          <t>{"Reference ID": "Q12238502"}</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -8119,7 +8251,7 @@
       <c r="T46" t="inlineStr"/>
       <c r="U46" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="V46" t="n">
@@ -8140,7 +8272,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>['1961-02-15']</t>
+          <t>['2000-01-01']</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -8150,12 +8282,12 @@
       </c>
       <c r="AD46" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Also Known As']</t>
+          <t>['Also Known As', 'Original Script Name']</t>
         </is>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
-          <t>['مسعود العامري', 'Masoud Bin Mohammed Al Ameri']</t>
+          <t>['Mubarak Bin Ali Al Khatir', 'مبارك بن علي آل خاطر']</t>
         </is>
       </c>
       <c r="AF46" t="inlineStr">
@@ -8195,12 +8327,12 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>['Civil Servant', 'Judge', 'Minister', 'Politician']</t>
+          <t>['Politician']</t>
         </is>
       </c>
       <c r="AN46" t="inlineStr">
         <is>
-          <t>['Judge']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
@@ -8232,7 +8364,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Sultan Bin Rashid Al Khater</t>
+          <t>Masoud Bin Mohammed Al Ameri</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
@@ -8241,7 +8373,11 @@
           <t>Male</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Qatari Politician</t>
+        </is>
+      </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
         <v>0</v>
@@ -8253,7 +8389,7 @@
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>{"Reference ID": "Q123091813"}</t>
+          <t>{"Educated At": "Cairo University, Faculty of medicine Cairo university", "Reference ID": "Q12242945"}</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -8276,11 +8412,7 @@
           <t>Individual</t>
         </is>
       </c>
-      <c r="R47" t="inlineStr">
-        <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/3/32/Sultan_bin_Rashid_Al-Khater_2022.jpg</t>
-        </is>
-      </c>
+      <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr">
         <is>
           <t>qa_gen</t>
@@ -8289,7 +8421,7 @@
       <c r="T47" t="inlineStr"/>
       <c r="U47" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="V47" t="n">
@@ -8310,12 +8442,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['1961-02-15']</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Qatar']</t>
         </is>
       </c>
       <c r="AD47" t="inlineStr">
@@ -8325,7 +8457,7 @@
       </c>
       <c r="AE47" t="inlineStr">
         <is>
-          <t>['Sultan Bin Rashid Al Khater']</t>
+          <t>['Masoud Bin Mohammed Al Ameri']</t>
         </is>
       </c>
       <c r="AF47" t="inlineStr">
@@ -8365,12 +8497,12 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Civil Servant', 'Judge', 'Minister', 'Politician']</t>
         </is>
       </c>
       <c r="AN47" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Judge']</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
@@ -8402,16 +8534,20 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Rabea Mechernane</t>
+          <t>Sultan Bin Rashid Al Khater</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr"/>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Undersecretary Of The Ministry Of Commerce And Industry, Qatar</t>
+        </is>
+      </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
         <v>0</v>
@@ -8423,7 +8559,7 @@
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>{"Reference ID": "Q123481131"}</t>
+          <t>{"Reference ID": "Q123091813"}</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -8446,7 +8582,11 @@
           <t>Individual</t>
         </is>
       </c>
-      <c r="R48" t="inlineStr"/>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>https://upload.wikimedia.org/wikipedia/commons/3/32/Sultan_bin_Rashid_Al-Khater_2022.jpg</t>
+        </is>
+      </c>
       <c r="S48" t="inlineStr">
         <is>
           <t>qa_gen</t>
@@ -8455,7 +8595,7 @@
       <c r="T48" t="inlineStr"/>
       <c r="U48" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="V48" t="n">
@@ -8481,17 +8621,17 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Qatar']</t>
         </is>
       </c>
       <c r="AD48" t="inlineStr">
         <is>
-          <t>['Also Known As']</t>
+          <t>['Also Known As', 'Also Known As']</t>
         </is>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
-          <t>['Rabea Mechernane']</t>
+          <t>['H E Sultan Bin Rashid Al Khater', 'Sultan Bin Rashid Al Khater']</t>
         </is>
       </c>
       <c r="AF48" t="inlineStr">
@@ -8531,7 +8671,7 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Politician']</t>
         </is>
       </c>
       <c r="AN48" t="inlineStr">
@@ -8568,16 +8708,20 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Sultan Bin Saad Bin Sultan Al Muraikhi</t>
+          <t>Rabea Mechernane</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr"/>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Algerian-Qatari Womens Rights Activist And Politician</t>
+        </is>
+      </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
         <v>0</v>
@@ -8589,7 +8733,7 @@
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>{"Academic Degree": "bachelors degree in political science", "Reference ID": "Q124705613"}</t>
+          <t>{"Reference ID": "Q123481131"}</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -8612,11 +8756,7 @@
           <t>Individual</t>
         </is>
       </c>
-      <c r="R49" t="inlineStr">
-        <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/6/60/Συνάντηση_ΥΠΕΞ_Γιώργου_Γεραπετρίτη_με_Υπουργό_Επικρατείας_Κατάρ,_αρμόδιο_για_Εξωτερικές_Υποθέσεις_Al_Muraikhi_(Μουσκάτ,_9-10.10.2023)_(cropped).jpg</t>
-        </is>
-      </c>
+      <c r="R49" t="inlineStr"/>
       <c r="S49" t="inlineStr">
         <is>
           <t>qa_gen</t>
@@ -8625,7 +8765,7 @@
       <c r="T49" t="inlineStr"/>
       <c r="U49" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="V49" t="n">
@@ -8651,17 +8791,17 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Algeria', 'Qatar']</t>
         </is>
       </c>
       <c r="AD49" t="inlineStr">
         <is>
-          <t>['Original Script Name']</t>
+          <t>['Also Known As']</t>
         </is>
       </c>
       <c r="AE49" t="inlineStr">
         <is>
-          <t>['سلطان بن سعد المريخي']</t>
+          <t>['Rabea Mechernane']</t>
         </is>
       </c>
       <c r="AF49" t="inlineStr">
@@ -8701,7 +8841,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Activist', 'Politician']</t>
         </is>
       </c>
       <c r="AN49" t="inlineStr">
@@ -8738,14 +8878,10 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Mohammed Bin Khalifa Al Thani</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Khalifa Bin Hamad Al Thani</t>
-        </is>
-      </c>
+          <t>Sultan Bin Saad Bin Sultan Al Muraikhi</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
           <t>Male</t>
@@ -8753,14 +8889,10 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Member Of The Royal Family Of Qatar (Born 1965)</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Doha</t>
-        </is>
-      </c>
+          <t>Qatari Politician</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
         <v>0</v>
       </c>
@@ -8771,7 +8903,7 @@
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>{"Educated At": "George Washington University", "Reference ID": "Q130215643"}</t>
+          <t>{"Academic Degree": "bachelors degree in political science", "Reference ID": "Q124705613"}</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -8794,7 +8926,11 @@
           <t>Individual</t>
         </is>
       </c>
-      <c r="R50" t="inlineStr"/>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>https://upload.wikimedia.org/wikipedia/commons/6/60/Συνάντηση_ΥΠΕΞ_Γιώργου_Γεραπετρίτη_με_Υπουργό_Επικρατείας_Κατάρ,_αρμόδιο_για_Εξωτερικές_Υποθέσεις_Al_Muraikhi_(Μουσκάτ,_9-10.10.2023)_(cropped).jpg</t>
+        </is>
+      </c>
       <c r="S50" t="inlineStr">
         <is>
           <t>qa_gen</t>
@@ -8803,7 +8939,7 @@
       <c r="T50" t="inlineStr"/>
       <c r="U50" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="V50" t="n">
@@ -8824,7 +8960,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>['1965-01-01']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
@@ -8839,7 +8975,7 @@
       </c>
       <c r="AE50" t="inlineStr">
         <is>
-          <t>['محمد بن خليفة آل ثاني']</t>
+          <t>['سلطان بن سعد المريخي']</t>
         </is>
       </c>
       <c r="AF50" t="inlineStr">
@@ -8879,7 +9015,7 @@
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Diplomat', 'Politician']</t>
         </is>
       </c>
       <c r="AN50" t="inlineStr">
@@ -8899,12 +9035,12 @@
       </c>
       <c r="AQ50" t="inlineStr">
         <is>
-          <t>['Sibling']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AR50" t="inlineStr">
         <is>
-          <t>['QA-GEN-HBKAT-0TKTJ-RCA-1']</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -8916,15 +9052,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Abdullah Hassan Al Sulaiti</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
+          <t>Mohammed Bin Khalifa Al Thani</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Khalifa Bin Hamad Al Thani</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Member Of The Royal Family Of Qatar (Born 1965)</t>
+        </is>
+      </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>Doha</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8937,7 +9085,7 @@
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>{"Reference ID": "Q130755981"}</t>
+          <t>{"Educated At": "George Washington University", "Reference ID": "Q130215643"}</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -8960,11 +9108,7 @@
           <t>Individual</t>
         </is>
       </c>
-      <c r="R51" t="inlineStr">
-        <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/8/86/Abdullah_Hassan_Al-_Sulaiti_(210915-N-TR763-2083)_(cropped).jpg</t>
-        </is>
-      </c>
+      <c r="R51" t="inlineStr"/>
       <c r="S51" t="inlineStr">
         <is>
           <t>qa_gen</t>
@@ -8973,7 +9117,7 @@
       <c r="T51" t="inlineStr"/>
       <c r="U51" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="V51" t="n">
@@ -8994,22 +9138,22 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['1965-01-01']</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Qatar']</t>
         </is>
       </c>
       <c r="AD51" t="inlineStr">
         <is>
-          <t>['Also Known As']</t>
+          <t>['Original Script Name']</t>
         </is>
       </c>
       <c r="AE51" t="inlineStr">
         <is>
-          <t>['Abdullah Hassan Al Sulaiti']</t>
+          <t>['محمد بن خليفة آل ثاني']</t>
         </is>
       </c>
       <c r="AF51" t="inlineStr">
@@ -9049,7 +9193,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Civil Servant', 'Politician']</t>
         </is>
       </c>
       <c r="AN51" t="inlineStr">
@@ -9069,12 +9213,12 @@
       </c>
       <c r="AQ51" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Sibling']</t>
         </is>
       </c>
       <c r="AR51" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['QA-GEN-HBKAT-0TKTJ-RCA-1']</t>
         </is>
       </c>
     </row>
@@ -9086,23 +9230,15 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Khalid Bin Mohammad Al Attiyah</t>
+          <t>Abdullah Hassan Al Sulaiti</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Qatari Politician</t>
-        </is>
-      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Doha</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -9115,7 +9251,7 @@
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>{"Educated At": "Beirut Arab University, Cairo University, King Faisal Air Academy", "Reference ID": "Q13560046"}</t>
+          <t>{"Reference ID": "Q130755981"}</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -9140,7 +9276,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/a/ae/Khalid_bin_Mohammad_Al_Attiyah_at_Al_Udeid_Air_Base,_Qatar_on_19_December_2023_-_(cropped).jpg</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/8/86/Abdullah_Hassan_Al-_Sulaiti_(210915-N-TR763-2083)_(cropped).jpg</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -9151,7 +9287,7 @@
       <c r="T52" t="inlineStr"/>
       <c r="U52" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="V52" t="n">
@@ -9172,7 +9308,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>['1967-03-09']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
@@ -9182,12 +9318,12 @@
       </c>
       <c r="AD52" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Also Known As']</t>
+          <t>['Also Known As']</t>
         </is>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
-          <t>['خالد بن محمد العطية', 'ハリド・アル・アティーヤ', 'خالد بن محمد العطیه', 'Jalid Bin Mohammad Al Attiyah', "ח'אלד בן מוחמד אל עטיה", 'ハリド・ビン・モハマド・アル・アティヤ', 'خالد بن محمد العطيه', 'Khalid Bin Mohammad Al Attiyah', 'Халед бен Мухаммед аль Атыйя', '哈立德·本·穆罕默德·阿勒阿提亚', 'Khalid Bin Muhammad Al Attiyah']</t>
+          <t>['Abdullah Hassan Al Sulaiti']</t>
         </is>
       </c>
       <c r="AF52" t="inlineStr">
@@ -9227,22 +9363,22 @@
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>['Diplomat', 'Entrepreneur', 'Military Personnel', 'Politician']</t>
+          <t>['Military Officer', 'Military Personnel']</t>
         </is>
       </c>
       <c r="AN52" t="inlineStr">
         <is>
-          <t>['Deputy Prime Minister Of Qatar', 'Minister Of Defence Of Qatar', 'Minister Of Foreign Affairs Of Qatar']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>['2016-01-27', '2016-01-27', '2013-06-26']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>[None, None, '2016-01-27']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AQ52" t="inlineStr">
@@ -9264,7 +9400,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Ali Al Thawadi</t>
+          <t>Khalid Bin Mohammad Al Attiyah</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
@@ -9273,8 +9409,16 @@
           <t>Male</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Qatari Politician</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Doha</t>
+        </is>
+      </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
@@ -9285,7 +9429,7 @@
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>{"Reference ID": "Q136466872"}</t>
+          <t>{"Educated At": "Beirut Arab University, Cairo University, King Faisal Air Academy", "Reference ID": "Q13560046"}</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -9308,7 +9452,11 @@
           <t>Individual</t>
         </is>
       </c>
-      <c r="R53" t="inlineStr"/>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>https://upload.wikimedia.org/wikipedia/commons/a/ae/Khalid_bin_Mohammad_Al_Attiyah_at_Al_Udeid_Air_Base,_Qatar_on_19_December_2023_-_(cropped).jpg</t>
+        </is>
+      </c>
       <c r="S53" t="inlineStr">
         <is>
           <t>qa_gen</t>
@@ -9317,7 +9465,7 @@
       <c r="T53" t="inlineStr"/>
       <c r="U53" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="V53" t="n">
@@ -9338,22 +9486,22 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['1967-03-09']</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Qatar']</t>
         </is>
       </c>
       <c r="AD53" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Original Script Name']</t>
+          <t>['Also Known As', 'Also Known As', 'Original Script Name']</t>
         </is>
       </c>
       <c r="AE53" t="inlineStr">
         <is>
-          <t>['علي الذوادي', "עלי א ת'וואדי"]</t>
+          <t>['Khalid Bin Mohammad Al Attiyah', 'Jalid Bin Mohammad Al Attiyah', 'ハリド・ビン・モハマド・アル・アティヤ']</t>
         </is>
       </c>
       <c r="AF53" t="inlineStr">
@@ -9393,22 +9541,22 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Diplomat', 'Entrepreneur', 'Military Personnel', 'Politician']</t>
         </is>
       </c>
       <c r="AN53" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Deputy Prime Minister Of Qatar', 'Minister Of Defence Of Qatar', 'Minister Of Foreign Affairs Of Qatar']</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['2016-01-27', '2016-01-27', '2013-06-26']</t>
         </is>
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[None, None, '2016-01-27']</t>
         </is>
       </c>
       <c r="AQ53" t="inlineStr">
@@ -9430,7 +9578,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Hassan Al Thawadi</t>
+          <t>Ali Al Thawadi</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
@@ -9441,7 +9589,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Secretary-General - Supreme Committee For Delivery And Legacy</t>
+          <t>Qatari Politician</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
@@ -9455,7 +9603,7 @@
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>{"Reference ID": "Q15814442"}</t>
+          <t>{"Reference ID": "Q136466872"}</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -9478,11 +9626,7 @@
           <t>Individual</t>
         </is>
       </c>
-      <c r="R54" t="inlineStr">
-        <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/3/31/Hassan_Al_Thawadi_-_30926598514.jpg</t>
-        </is>
-      </c>
+      <c r="R54" t="inlineStr"/>
       <c r="S54" t="inlineStr">
         <is>
           <t>qa_gen</t>
@@ -9491,7 +9635,7 @@
       <c r="T54" t="inlineStr"/>
       <c r="U54" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="V54" t="n">
@@ -9512,7 +9656,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>['1978-01-01']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
@@ -9522,12 +9666,12 @@
       </c>
       <c r="AD54" t="inlineStr">
         <is>
-          <t>['Also Known As', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name']</t>
+          <t>['Original Script Name']</t>
         </is>
       </c>
       <c r="AE54" t="inlineStr">
         <is>
-          <t>['Hassan Abdullah Al Thawadi', '哈桑·萨瓦迪', '哈桑·阿勒萨瓦迪', 'Hassan Al Thawadi', 'حسن الذوادي']</t>
+          <t>['["עלי א ת\'וואדי"]']</t>
         </is>
       </c>
       <c r="AF54" t="inlineStr">
@@ -9567,7 +9711,7 @@
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Politician']</t>
         </is>
       </c>
       <c r="AN54" t="inlineStr">
@@ -9604,14 +9748,10 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Tamim Bin Hamad Al</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Hamad Bin Khalifa Al Thani</t>
-        </is>
-      </c>
+          <t>Hassan Al Thawadi</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
           <t>Male</t>
@@ -9619,14 +9759,10 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Emir Of Qatar</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Doha</t>
-        </is>
-      </c>
+          <t>Secretary-General - Supreme Committee For Delivery And Legacy</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
       <c r="G55" t="n">
         <v>0</v>
       </c>
@@ -9637,7 +9773,7 @@
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>{"Educated At": "Harrow School, Royal Military Academy Sandhurst, Sherborne International, Sherborne School", "Reference ID": "Q1855372"}</t>
+          <t>{"Reference ID": "Q15814442"}</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -9662,7 +9798,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/4/49/Emir_of_Qatar_on_February_19,_2025_(cropped).jpg</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/3/31/Hassan_Al_Thawadi_-_30926598514.jpg</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
@@ -9673,7 +9809,7 @@
       <c r="T55" t="inlineStr"/>
       <c r="U55" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="V55" t="n">
@@ -9694,7 +9830,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>['1980-06-03']</t>
+          <t>['1978-01-01']</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
@@ -9704,12 +9840,12 @@
       </c>
       <c r="AD55" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Also Known As', 'Also Known As', 'Also Known As', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name']</t>
+          <t>['Also Known As', 'Original Script Name', 'Also Known As']</t>
         </is>
       </c>
       <c r="AE55" t="inlineStr">
         <is>
-          <t>['Tamím bin Hamad Ál Thání', 'تمیم بن حمد آل ثانی', 'تەمیم کوڕی حەمەدی دووەم', 'Tamim Bin Hamad Al Tsani', 'Тамім бін Хамад Аль Тані', 'Tamim Bin Hamad Bin Khalifa Al Thani', 'Тамим ибн Хамад ел Тани', 'Тамим ибн Хамад Аль Тани', 'タミーム・ビン・ハマド・アール＝サーニー', 'تَمِيم بِن حَمَد بِن خَلِيفَة آل ثَانِي', 'Tamim ibn Hàmad ibn Khalifa Al Thani', 'Temim Bin Hamed Es Sani', 'الشيخ تميم بن حمد ال ثاني', 'Temim Bin Hamad Es Sani', 'Temim Bin Hamad Al Sani', 'Sheikh Tamim Bin Hamad Bin Khalifa Al Thani Emir Of Qatar', 'Tamimas Bin Hamadas Al Tanis', 'Тамим бин Ҳамад Оли Танӣ', '따밈 빈 하마드 알 타니', 'Tamim Bin Hamad Al Thani', "תמים בן חמד אל ת'אני", '塔米姆', 'تمیم بن حمد الثانی', 'تمیم بن حمد بن خلیفه آل ثانی', 'タミーム', 'Təmim ibn Həməd Ali Sani', 'Tamīm ibn Ḩamad Āl Thānī', 'Tamim Ben Hamad Ben Khalifa Ben Hamad Ben Abdullah Ben Jassim Ben Mohammed Al Thani', 'Tamim Bin Hamad Al Tani', 'तमीम बिन हमद अल थानी', '塔米姆·本·哈邁德·阿勒薩尼', 'Tamimus Hamidi filius gentis Ṯānī', 'Ταμίμ μπιν Χαμάντ', 'Тамим бин Хамад ел Тани', 'ตะมีม บิน ฮะมัด อาล ษานี', '타밈 빈 하마드 알사니', '塔米姆·本·哈马德·阿勒萨尼', 'Tamím katari emír', 'Տամիմ Բին Համիդ Ալ Տհանի', 'თამიმ ბინ ჰამად ბინ ხალიფა ალ თანი', "השייח' תמים בן חמד השני", 'তামিম বিন হামাদ আল সানি', 'تَمیٖم بِن حَمَد آل ثانی"]', 'Tamim Bin Hamad', "תמים בן חמד אאל ת'אני", 'Tamim Ibn Hamad Al Sani', 'Тамим бин Хамад ал Тани', 'Tamim Ben Hamad Al Thani', 'Tamim bin Hamad Chalífa Sání', 'تميم بن حمد آل ثانى', "תמים בן חמד אאל ת'אני אמיר קטר", 'Éimír Chatar', 'Tamim I De Catar', 'تميم بن حمد آل ثاني']</t>
+          <t>['Hassan Al Thawadi', '哈桑·阿勒萨瓦迪', 'Hassan Abdullah Al Thawadi']</t>
         </is>
       </c>
       <c r="AF55" t="inlineStr">
@@ -9749,32 +9885,32 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>['Politician']</t>
+          <t>['Manager', 'Politician']</t>
         </is>
       </c>
       <c r="AN55" t="inlineStr">
         <is>
-          <t>['Crown Prince Of Qatar', 'Emir Of The State Of Qatar', 'Member Of The International Olympic Committee']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>['2003-08-05', '2013-06-25', '2002-01-01']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>['2013-06-25', None, None]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AQ55" t="inlineStr">
         <is>
-          <t>['Sibling', 'Sibling', 'Sibling', 'Sibling', 'Sibling', 'Sibling', 'Sibling', 'Sibling', 'Sibling', 'Sibling', 'Sibling', 'Partner', 'Partner', 'Partner', 'Mother', 'Relative', 'Relative']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AR55" t="inlineStr">
         <is>
-          <t>['QA-GEN-ABHBKAT-87DYX-RCA-1', 'QA-GEN-KBHBKAT-A7NJG-RCA-1', 'QA-GEN-MBHBKAT-XHR18-RCA-1', 'QA-GEN-MBHBKAT-LRHZY-RCA-1', 'QA-GEN-MBHBKAT-C3NWO-RCA-1', 'QA-GEN-PJBHOQ-PNKIK-RCA-1', 'QA-GEN-PJBHOQ-B78MR-RCA-1', 'QA-GEN-PKBHOQ-B6NQQ-RCA-1', 'QA-GEN-PAMBHOQ-3MSTL-RCA-1', 'QA-GEN-PHBHOQ-MJ0UC-RCA-1', 'QA-GEN-TBHAT-28KU2-RCA-1', 'QA-GEN-AABMAH-1KXBS-RCA-1', 'QA-GEN-JBHAT-EB0Z0-RCA-1', 'QA-GEN-NBHAD-JGB3R-RCA-1', 'QA-GEN-MBNAM-IN51I-RCA-1', 'QA-GEN-HBSAT-LEUBZ-RCA-1', 'QA-GEN-KBHAT-ND19D-RCA-1']</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -9786,10 +9922,14 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Wissam Al Mana</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr"/>
+          <t>Tamim Bin Hamad Al</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Hamad Bin Khalifa Al Thani</t>
+        </is>
+      </c>
       <c r="D56" t="inlineStr">
         <is>
           <t>Male</t>
@@ -9797,7 +9937,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Qatari Businessman</t>
+          <t>Emir Of Qatar</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -9815,7 +9955,7 @@
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>{"Educated At": "George Washington University, London School of Economics and Political Science", "Reference ID": "Q19609519"}</t>
+          <t>{"Educated At": "Harrow School, Royal Military Academy Sandhurst, Sherborne International, Sherborne School", "Reference ID": "Q1855372"}</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -9838,7 +9978,11 @@
           <t>Individual</t>
         </is>
       </c>
-      <c r="R56" t="inlineStr"/>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>https://upload.wikimedia.org/wikipedia/commons/4/49/Emir_of_Qatar_on_February_19,_2025_(cropped).jpg</t>
+        </is>
+      </c>
       <c r="S56" t="inlineStr">
         <is>
           <t>qa_gen</t>
@@ -9847,7 +9991,7 @@
       <c r="T56" t="inlineStr"/>
       <c r="U56" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="V56" t="n">
@@ -9868,7 +10012,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>['1975-01-01']</t>
+          <t>['1980-06-03']</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
@@ -9878,12 +10022,12 @@
       </c>
       <c r="AD56" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As']</t>
+          <t>['Also Known As', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Also Known As', 'Also Known As', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As']</t>
         </is>
       </c>
       <c r="AE56" t="inlineStr">
         <is>
-          <t>['وسام المانع', '威萨姆·阿尔·马纳', '威薩姆·阿爾·馬納', 'Γουισάμ Αλ Μάνα', 'Wissam Al Mana']</t>
+          <t>['Temim Bin Hamad Al Sani', 'Tamim ibn Hàmad ibn Khalifa Al Thani', 'Sheikh Tamim Bin Hamad Bin Khalifa Al Thani Emir Of Qatar', 'Tamim bin Hamad Chalífa Sání', 'Tamim Bin Hamad Bin Khalifa Al Thani', 'Tamim I De Catar', 'Tamim Bin Hamad Al Thani', "תמים בן חמד אאל ת'אני אמיר קטר", "תמים בן חמד אל ת'אני", 'Temim Bin Hamad Es Sani', 'تَمِيم بِن حَمَد بِن خَلِيفَة آل ثَانِي', 'Tamim Ben Hamad Al Thani', 'Təmim ibn Həməd Ali Sani', "השייח' תמים בן חמד השני", 'Éimír Chatar', 'タミーム', 'الشيخ تميم بن حمد ال ثاني', 'Tamim Ben Hamad Ben Khalifa Ben Hamad Ben Abdullah Ben Jassim Ben Mohammed Al Thani']</t>
         </is>
       </c>
       <c r="AF56" t="inlineStr">
@@ -9923,32 +10067,32 @@
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Politician']</t>
         </is>
       </c>
       <c r="AN56" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Crown Prince Of Qatar', 'Emir Of The State Of Qatar', 'Member Of The International Olympic Committee']</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['2003-08-05', '2013-06-25', '2002-01-01']</t>
         </is>
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['2013-06-25', None, None]</t>
         </is>
       </c>
       <c r="AQ56" t="inlineStr">
         <is>
-          <t>['Partner', 'Child']</t>
+          <t>['Sibling', 'Sibling', 'Sibling', 'Sibling', 'Sibling', 'Sibling', 'Sibling', 'Sibling', 'Sibling', 'Sibling', 'Sibling', 'Relative', 'Relative', 'Partner', 'Partner', 'Partner', 'Mother']</t>
         </is>
       </c>
       <c r="AR56" t="inlineStr">
         <is>
-          <t>['QA-GEN-JJ-OM38T-RCA-1', 'QA-GEN-EAM-L9PZJ-RCA-1']</t>
+          <t>['QA-GEN-ABHBKAT-87DYX-RCA-1', 'QA-GEN-KBHBKAT-A7NJG-RCA-1', 'QA-GEN-MBHBKAT-XHR18-RCA-1', 'QA-GEN-MBHBKAT-LRHZY-RCA-1', 'QA-GEN-MBHBKAT-C3NWO-RCA-1', 'QA-GEN-PJBHOQ-PNKIK-RCA-1', 'QA-GEN-PJBHOQ-B78MR-RCA-1', 'QA-GEN-PKBHOQ-B6NQQ-RCA-1', 'QA-GEN-PAMBHOQ-3MSTL-RCA-1', 'QA-GEN-PHBHOQ-MJ0UC-RCA-1', 'QA-GEN-TBHAT-28KU2-RCA-1', 'QA-GEN-HBSAT-LEUBZ-RCA-1', 'QA-GEN-KBHAT-ND19D-RCA-1', 'QA-GEN-AABMAH-1KXBS-RCA-1', 'QA-GEN-JBHAT-EB0Z0-RCA-1', 'QA-GEN-NBHAD-JGB3R-RCA-1', 'QA-GEN-MBNAM-IN51I-RCA-1']</t>
         </is>
       </c>
     </row>
@@ -9960,7 +10104,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Abdulla Bin Mohammed Bin Saud Al Thani</t>
+          <t>Wissam Al Mana</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
@@ -9971,10 +10115,14 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Qatari Businessman And Politician</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr"/>
+          <t>Qatari Businessman</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Doha</t>
+        </is>
+      </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
@@ -9985,7 +10133,7 @@
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>{"Reference ID": "Q19661549"}</t>
+          <t>{"Educated At": "George Washington University, London School of Economics and Political Science", "Reference ID": "Q19609519"}</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -10008,11 +10156,7 @@
           <t>Individual</t>
         </is>
       </c>
-      <c r="R57" t="inlineStr">
-        <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/5/55/Steven_Mnuchin_meets_with_Abdulla_Bin_Saoud_Al-Thani_at_Doha.jpg</t>
-        </is>
-      </c>
+      <c r="R57" t="inlineStr"/>
       <c r="S57" t="inlineStr">
         <is>
           <t>qa_gen</t>
@@ -10021,7 +10165,7 @@
       <c r="T57" t="inlineStr"/>
       <c r="U57" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="V57" t="n">
@@ -10042,7 +10186,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>['1959-11-20']</t>
+          <t>['1975-01-01']</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
@@ -10052,12 +10196,12 @@
       </c>
       <c r="AD57" t="inlineStr">
         <is>
-          <t>['Also Known As', 'Also Known As', 'Original Script Name', 'Also Known As', 'Also Known As', 'Also Known As', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As']</t>
+          <t>['Also Known As']</t>
         </is>
       </c>
       <c r="AE57" t="inlineStr">
         <is>
-          <t>['Abdullah Bin Mohammed Bin Saud Al Thani', 'Abdullah Bin Saoud Al Thani', 'عبدالله بن محمد بن سعود آل ثاني', 'Abdullah Saoud Al Thani', 'Abdullah Bin Mohammed Al Thani', 'Abdulla Bin Mohammed Bin Saud Al Thani', 'Abdulla Bin Mohammed Al Thani', 'عبد الله بن محمد بن سعود آل ثاني', 'عبدالله بن محمد بن سعود آلثانی', 'Աբդուլլահ բին Մոհամմեդ Ալ Թանի', 'H E Sheikh Abdullah Bin Mohammed Al Thani']</t>
+          <t>['Wissam Al Mana']</t>
         </is>
       </c>
       <c r="AF57" t="inlineStr">
@@ -10097,7 +10241,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Businessperson']</t>
         </is>
       </c>
       <c r="AN57" t="inlineStr">
@@ -10117,12 +10261,12 @@
       </c>
       <c r="AQ57" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Child', 'Partner']</t>
         </is>
       </c>
       <c r="AR57" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['QA-GEN-EAM-L9PZJ-RCA-1', 'QA-GEN-JJ-OM38T-RCA-1']</t>
         </is>
       </c>
     </row>
@@ -10134,29 +10278,21 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Alya Ahmed Saif Al Thani</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ahmed Bin Saif Al Thani</t>
-        </is>
-      </c>
+          <t>Abdulla Bin Mohammed Bin Saud Al Thani</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Qatari Diplomat</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Doha</t>
-        </is>
-      </c>
+          <t>Qatari Businessman And Politician</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
       <c r="G58" t="n">
         <v>0</v>
       </c>
@@ -10167,7 +10303,7 @@
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>{"Educated At": "Qatar University, SOAS, University of London", "Reference ID": "Q19664610"}</t>
+          <t>{"Reference ID": "Q19661549"}</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -10192,7 +10328,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/d/d0/Special_event_-_Panel_discussion,_Mainstreaming_Sustainability_into_Trade_and_Development_Policies_Towards_the_Rio+20_Summit_(7112264733).jpg</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/9/9a/Abdullah_Bin_Mohammed_Bin_Saud_Al_Thani.png</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
@@ -10203,7 +10339,7 @@
       <c r="T58" t="inlineStr"/>
       <c r="U58" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="V58" t="n">
@@ -10224,7 +10360,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>['1974-01-01']</t>
+          <t>['1959-11-20']</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
@@ -10234,12 +10370,12 @@
       </c>
       <c r="AD58" t="inlineStr">
         <is>
-          <t>['Also Known As', 'Also Known As', 'Also Known As', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name', 'Original Script Name']</t>
+          <t>['Original Script Name', 'Also Known As', 'Also Known As', 'Also Known As', 'Also Known As', 'Also Known As']</t>
         </is>
       </c>
       <c r="AE58" t="inlineStr">
         <is>
-          <t>['Alya Al Thani', 'Alia Bint Ahmed Bin Saif Al Thani', 'Alya Bint Ahmed Bin Saif Al Thani', 'Alia Ahmad Al Thani', 'علياء أحمد سيف آل ثاني', 'علیا آل ثانی', 'Sheikha Alya Bint Ahmed Al Thani', 'அல்யா பின்த் அகமது அல் தானி', 'علياء آل ثاني', 'Алия Аль Тани', 'علیا بنت احمد آل ثانی', 'Алия аль Тани', 'الشيخة علياء أحمد سيف آل ثاني', 'Sheikha Alya Ahmed Bint Saif Al Thani', 'Alia Bint Ahmed Al Thani', "עליאא בנת אחמד אאל ת'אני", 'Sheikha Alia Ahmad Al Thani', 'Alya Bint Ahmed Al Thani', 'আলিয়া বিনতে আহমেদ আল থানি', 'Sheikha Alya Ahmed Saif Al Thani', 'Alya Ahmed Saif Al Thani', 'Алія Аль Сані', 'Аль Тани Алия']</t>
+          <t>['عبدالله بن محمد بن سعود آل ثاني', 'Abdulla Bin Mohammed Al Thani', 'Abdullah Saoud Al Thani', 'H E Sheikh Abdullah Bin Mohammed Al Thani', 'Abdullah Bin Mohammed Al Thani', 'Abdulla Bin Mohammed Bin Saud Al Thani']</t>
         </is>
       </c>
       <c r="AF58" t="inlineStr">
@@ -10279,7 +10415,7 @@
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Politician']</t>
         </is>
       </c>
       <c r="AN58" t="inlineStr">
@@ -10316,22 +10452,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Abdullah Bin Hamad Bin Khalifa Al Thani</t>
+          <t>Alya Ahmed Saif Al Thani</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Hamad Bin Khalifa Al Thani</t>
+          <t>Ahmed Bin Saif Al Thani</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Qatari Politician</t>
+          <t>Qatari Diplomat</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -10349,7 +10485,7 @@
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>{"Educated At": "Qatar Academy, Walsh School of Foreign Service", "Reference ID": "Q19665019"}</t>
+          <t>{"Educated At": "Qatar University, SOAS, University of London", "Reference ID": "Q19664610"}</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -10374,7 +10510,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/0/05/Sheikh_abdualla_althani.jpg</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/d/d0/Special_event_-_Panel_discussion,_Mainstreaming_Sustainability_into_Trade_and_Development_Policies_Towards_the_Rio+20_Summit_(7112264733).jpg</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -10385,7 +10521,7 @@
       <c r="T59" t="inlineStr"/>
       <c r="U59" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="V59" t="n">
@@ -10406,7 +10542,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>['1988-02-09']</t>
+          <t>['1974-01-01']</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
@@ -10416,12 +10552,12 @@
       </c>
       <c r="AD59" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Also Known As', 'Also Known As', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name']</t>
+          <t>['Original Script Name', 'Also Known As', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Also Known As', 'Also Known As', 'Also Known As', 'Also Known As']</t>
         </is>
       </c>
       <c r="AE59" t="inlineStr">
         <is>
-          <t>['Abdullah bin Hamad bin Chalífa Ál Thání', 'আবদুল্লাহ বিন হামাদ বিন খলিফা আল থানি', 'Abduallah Althani', 'عبدالله بن حمد آل ثاني', 'アブドゥッラー', '阿卜杜拉·本·哈馬德·本·哈利法·阿勒薩尼', 'Abdullah bin Hamad bin Ĥalifa Al Thani', 'Abdullah Bin Hamad Al Thani', "עבדאללה בן חמד אאל ת'אני", 'Abdullah Bin Hamad Al Tsani', 'アブドゥッラー・ビン・ハマド・アール＝サーニー', 'Abdullah Bin Hamad Bin Khalifa Al Thani', 'Abdallah Ben Hamad Al Thani', 'Sheikh Abdualla Althani', 'アブドゥッラー・ビン・ハマド・ビン・ハリーファ・アール＝サーニー', 'عبدالله بن حمد بن خلیفه آل ثانی', 'Абдаллах ибн Хамад Аль Тани', 'Աբդուլլահ Բին Համադ Բին Խալիֆա Ալ Տհանի', 'アブドッラー・ビン・ハマド・アール＝サーニー', 'عبد الله بن حمد آل ثاني', 'عبد اللہ بن حمد آل ثانی']</t>
+          <t>['Аль Тани Алия', 'Alya Al Thani', 'الشيخة علياء أحمد سيف آل ثاني', 'Alya Ahmed Saif Al Thani', 'علیا آل ثانی', 'Sheikha Alya Ahmed Saif Al Thani', 'Sheikha Alya Bint Ahmed Al Thani', 'Алия аль Тани', 'Alya Bint Ahmed Bin Saif Al Thani', 'Alia Bint Ahmed Al Thani', 'علياء آل ثاني', 'علياء أحمد سيف آل ثاني', 'Alia Ahmad Al Thani', 'Alya Bint Ahmed Al Thani', 'Sheikha Alya Ahmed Bint Saif Al Thani', 'Sheikha Alia Ahmad Al Thani', 'Alia Bint Ahmed Bin Saif Al Thani']</t>
         </is>
       </c>
       <c r="AF59" t="inlineStr">
@@ -10461,12 +10597,12 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>['Politician']</t>
+          <t>['Diplomat', 'Politician']</t>
         </is>
       </c>
       <c r="AN59" t="inlineStr">
         <is>
-          <t>['Crown Prince']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
@@ -10481,12 +10617,12 @@
       </c>
       <c r="AQ59" t="inlineStr">
         <is>
-          <t>['Sibling']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AR59" t="inlineStr">
         <is>
-          <t>['QA-GEN-TBHA-K036O-RCA-1']</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -10498,17 +10634,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Maha Mansour Salman Jassim Al Thani</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr"/>
+          <t>Abdullah Bin Hamad Bin Khalifa Al Thani</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Hamad Bin Khalifa Al Thani</t>
+        </is>
+      </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Qatari Politician</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Doha</t>
+        </is>
+      </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
@@ -10519,7 +10667,7 @@
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>{"Reference ID": "Q20422692"}</t>
+          <t>{"Educated At": "Qatar Academy, Walsh School of Foreign Service", "Reference ID": "Q19665019"}</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -10542,7 +10690,11 @@
           <t>Individual</t>
         </is>
       </c>
-      <c r="R60" t="inlineStr"/>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>https://upload.wikimedia.org/wikipedia/commons/0/05/Sheikh_abdualla_althani.jpg</t>
+        </is>
+      </c>
       <c r="S60" t="inlineStr">
         <is>
           <t>qa_gen</t>
@@ -10551,7 +10703,7 @@
       <c r="T60" t="inlineStr"/>
       <c r="U60" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="V60" t="n">
@@ -10572,22 +10724,22 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['1988-02-09']</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Qatar']</t>
         </is>
       </c>
       <c r="AD60" t="inlineStr">
         <is>
-          <t>['Also Known As', 'Original Script Name', 'Also Known As']</t>
+          <t>['Original Script Name', 'Also Known As', 'Also Known As', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name']</t>
         </is>
       </c>
       <c r="AE60" t="inlineStr">
         <is>
-          <t>['Sheikha Maha Mansour Al Thani', 'مها منصور سلمان جاسم آل ثاني', 'Maha Mansour Salman Jassim Al Thani']</t>
+          <t>['アブドゥッラー・ビン・ハマド・ビン・ハリーファ・アール＝サーニー', 'Sheikh Abdualla Althani', 'Abdallah Ben Hamad Al Thani', 'Abduallah Althani', 'アブドゥッラー・ビン・ハマド・アール＝サーニー', 'عبدالله بن حمد آل ثاني', 'アブドゥッラー']</t>
         </is>
       </c>
       <c r="AF60" t="inlineStr">
@@ -10627,12 +10779,12 @@
       </c>
       <c r="AM60" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Politician']</t>
         </is>
       </c>
       <c r="AN60" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Crown Prince']</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
@@ -10647,12 +10799,12 @@
       </c>
       <c r="AQ60" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Sibling']</t>
         </is>
       </c>
       <c r="AR60" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['QA-GEN-TBHA-K036O-RCA-1']</t>
         </is>
       </c>
     </row>
@@ -10664,16 +10816,20 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Ahmad Bin Eid Al Thani</t>
+          <t>Maha Mansour Salman Jassim Al Thani</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr"/>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Qatari Politician</t>
+        </is>
+      </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
         <v>0</v>
@@ -10685,7 +10841,7 @@
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>{"Reference ID": "Q22949042"}</t>
+          <t>{"Reference ID": "Q20422692"}</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -10717,7 +10873,7 @@
       <c r="T61" t="inlineStr"/>
       <c r="U61" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="V61" t="n">
@@ -10743,17 +10899,17 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Qatar']</t>
         </is>
       </c>
       <c r="AD61" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Also Known As']</t>
+          <t>['Also Known As', 'Also Known As']</t>
         </is>
       </c>
       <c r="AE61" t="inlineStr">
         <is>
-          <t>['أحمد بن عيد آل ثاني', 'Ahmad Bin Eid Al Thani']</t>
+          <t>['Sheikha Maha Mansour Al Thani', 'Maha Mansour Salman Jassim Al Thani']</t>
         </is>
       </c>
       <c r="AF61" t="inlineStr">
@@ -10793,12 +10949,12 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Judge', 'Lawyer', 'Politician']</t>
         </is>
       </c>
       <c r="AN61" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Judge']</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
@@ -10830,7 +10986,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Mohammed Bin Abdulrahman Al Thani</t>
+          <t>Ahmad Bin Eid Al Thani</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
@@ -10841,14 +10997,10 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Prime Minister And The Minister Of Foreign Affairs Of Qatar</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Doha</t>
-        </is>
-      </c>
+          <t>Politician</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
         <v>0</v>
       </c>
@@ -10859,7 +11011,7 @@
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>{"Educated At": "Qatar University", "Reference ID": "Q23020336"}</t>
+          <t>{"Reference ID": "Q22949042"}</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -10882,11 +11034,7 @@
           <t>Individual</t>
         </is>
       </c>
-      <c r="R62" t="inlineStr">
-        <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/9/97/Mohammed_bin_Abdulrahman_Al-Thani_of_Qatar_on_25_January_2024_-_2_(cropped).jpg</t>
-        </is>
-      </c>
+      <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr">
         <is>
           <t>qa_gen</t>
@@ -10895,7 +11043,7 @@
       <c r="T62" t="inlineStr"/>
       <c r="U62" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="V62" t="n">
@@ -10916,7 +11064,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>['1980-11-01']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
@@ -10926,12 +11074,12 @@
       </c>
       <c r="AD62" t="inlineStr">
         <is>
-          <t>['Also Known As', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Also Known As', 'Original Script Name']</t>
+          <t>['Also Known As']</t>
         </is>
       </c>
       <c r="AE62" t="inlineStr">
         <is>
-          <t>['Mohammed Ben Abderrahmane Al Thani', 'Магамэд бін Абдулрагман Аль Тані', 'His Excellency Mohammed Bin Abdulrahman Bin Jassim Al Thani', 'मुहम्मद बिन अब्दुर्रहमान बिन जासिम अल सानी', 'Мөхәммәт бин Абдулрахман бин Җассим Аль Тани', 'Sheikh Mohammed Bin Abdulrahman Al Thani', 'ムハンマド・ビン・アブドゥッラフマーン・アール・サーニー', '穆罕默德·本·阿卜杜勒拉赫曼·阿勒萨尼', 'ムハンマド・ビン・アブドルラフマン・アール・サーニー', 'Mohammed Bin Abdulrahman Bin Jassim Al Thani', 'محمد بن عبدالرحمن بن جاسم الثانی', '穆罕默德·本·阿卜杜拉赫曼·阿勒萨尼', 'عبد الرحمن بن جاسم بن محمد آل ثاني', 'ムハンマド・ビン・アブドゥルラフマン・アール・サーニー', 'محمد بن عبدالرحمن آل ثانی', 'Mahometus ʿAbd al Raḥmān filius gentis Ṯānī', 'Muhammad bin Abdar Rahmán Sání', 'Мохаммед бин Абдулрахман бин Джассим Аль Тани', 'Muhammad Ibn Abdul Rahman Al Thani', 'محمد بن عبد الرحمن آل ثاني', 'Muhammed Bin Abdurrahman Es Sani', 'ムハンマド・ビン・アブドゥルラフマン・ビン・ジャシム・アル＝サーニー', 'Μοχάμεντ μπιν Αμπντουλραμάν μπιν Τζασίμ Αλ Θανί', 'Mohammed Bin Abdulrahman Al Thani', '穆罕默德·本·阿卜杜拉赫曼·本·贾西姆·阿勒萨尼', 'محمد بن عبد الرحمن آل ثانى', '穆罕默德·本·阿蔔杜勒拉赫曼·阿勒薩尼', 'মোহাম্মদ বিন আব্দুর রহমান বিন জসিম আলে সানি', 'ムハンマド・ビン・アブドゥッラフマーン・アール＝サーニー', "מוחמד בן עבד א רחמן בן ג'אסם אאל ת'אני", 'Abdulrahman Bin Jassim Bin Mohammed Al Thani', 'محمد بن عبدالرحمن آل ثاني', 'Mohammed Bin Abdul Rahman Al Thani', 'ムハンマド・ビン・アブドゥルラフマン・アール＝サーニー']</t>
+          <t>['Ahmad Bin Eid Al Thani']</t>
         </is>
       </c>
       <c r="AF62" t="inlineStr">
@@ -10971,32 +11119,32 @@
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>['Diplomat', 'Economist', 'Politician']</t>
+          <t>['Politician']</t>
         </is>
       </c>
       <c r="AN62" t="inlineStr">
         <is>
-          <t>['Deputy Prime Minister Of Qatar', 'Minister Of Foreign Affairs Of Qatar', 'Prime Minister Of Qatar', 'Ambassador Of Qatar To Jordan', 'Independent Politician']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>['2016-01-27', '2016-01-27', '2023-03-07', '2000-01-01']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>['2023-03-07', None, None, '2003-01-01']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AQ62" t="inlineStr">
         <is>
-          <t>['Relative']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AR62" t="inlineStr">
         <is>
-          <t>['QA-GEN-HBJBJAT-W665T-RCA-1']</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -11008,7 +11156,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Ali Bin Saeed Bin Smaikh Al Marri</t>
+          <t>Mohammed Bin Abdulrahman Al Thani</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
@@ -11019,10 +11167,14 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Minister Of Labor In Qatar</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr"/>
+          <t>Prime Minister And The Minister Of Foreign Affairs Of Qatar</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Doha</t>
+        </is>
+      </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
@@ -11033,7 +11185,7 @@
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>{"Reference ID": "Q24851512"}</t>
+          <t>{"Educated At": "Qatar University", "Reference ID": "Q23020336"}</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -11058,7 +11210,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/d/d7/Portrait_of_Ali_bin_Samikh_Al_Marri_at_the_Seventh_Abu_Dhabi_Dialogue_(ADD)_Ministerial_Consultation_in_Dubai.png</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/9/97/Mohammed_bin_Abdulrahman_Al-Thani_of_Qatar_on_25_January_2024_-_2_(cropped).jpg</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
@@ -11069,7 +11221,7 @@
       <c r="T63" t="inlineStr"/>
       <c r="U63" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="V63" t="n">
@@ -11090,7 +11242,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>['1972-11-30']</t>
+          <t>['1980-11-01']</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
@@ -11100,12 +11252,12 @@
       </c>
       <c r="AD63" t="inlineStr">
         <is>
-          <t>['Also Known As', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Also Known As', 'Also Known As']</t>
+          <t>['Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name']</t>
         </is>
       </c>
       <c r="AE63" t="inlineStr">
         <is>
-          <t>['Ali Bin Saeed Bin Samikh Al Marri', 'علي بن سعيد بن صميخ المرّي', 'علی بن سعید بن صمیخ المری', 'Ali Bin Said Bin Smaikh Break Al Owair Al Marri', 'علي بن صميخ المري', 'He Dr Ali Bin Saeed Bin Smaikh Al Marri', 'Ali Bin Samikh Al Marri']</t>
+          <t>['Mohammed Bin Abdulrahman Bin Jassim Al Thani', 'عبد الرحمن بن جاسم بن محمد آل ثاني', '穆罕默德·本·阿卜杜拉赫曼·本·贾西姆·阿勒萨尼', "['Mahometus ʿAbd al Raḥmān filius gentis Ṯānī']", 'محمد بن عبد الرحمن آل ثاني', 'ムハンマド・ビン・アブドゥルラフマン・ビン・ジャシム・アル＝サーニー', 'Abdulrahman Bin Jassim Bin Mohammed Al Thani', 'ムハンマド・ビン・アブドゥッラフマーン・アール・サーニー', 'ムハンマド・ビン・アブドルラフマン・アール・サーニー', 'Sheikh Mohammed Bin Abdulrahman Al Thani', 'His Excellency Mohammed Bin Abdulrahman Bin Jassim Al Thani', 'ムハンマド・ビン・アブドゥルラフマン・アール＝サーニー', 'محمد بن عبدالرحمن آل ثاني', 'Mohammed Bin Abdulrahman Al Thani', '穆罕默德·本·阿卜杜拉赫曼·阿勒萨尼', 'ムハンマド・ビン・アブドゥッラフマーン・アール＝サーニー']</t>
         </is>
       </c>
       <c r="AF63" t="inlineStr">
@@ -11145,32 +11297,32 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>['Academic', 'Minister', 'Official', 'Politician']</t>
+          <t>['Diplomat', 'Economist', 'Politician']</t>
         </is>
       </c>
       <c r="AN63" t="inlineStr">
         <is>
-          <t>['Minister Of Labour']</t>
+          <t>['Deputy Prime Minister Of Qatar', 'Minister Of Foreign Affairs Of Qatar', 'Prime Minister Of Qatar', 'Ambassador Of Qatar To Jordan', 'Independent Politician']</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>['2021-10-19']</t>
+          <t>['2016-01-27', '2016-01-27', '2023-03-07', '2000-01-01']</t>
         </is>
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>[None]</t>
+          <t>['2023-03-07', None, None, '2003-01-01']</t>
         </is>
       </c>
       <c r="AQ63" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Relative']</t>
         </is>
       </c>
       <c r="AR63" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['QA-GEN-HBJBJAT-W665T-RCA-1']</t>
         </is>
       </c>
     </row>
@@ -11182,7 +11334,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Abdullah Bin Hamad Al Attiyah</t>
+          <t>Ali Bin Saeed Bin Smaikh Al Marri</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
@@ -11193,14 +11345,10 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Doha</t>
-        </is>
-      </c>
+          <t>Minister Of Labor In Qatar</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
         <v>0</v>
       </c>
@@ -11211,7 +11359,7 @@
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>{"Educated At": "Alexandria University", "Reference ID": "Q2820939"}</t>
+          <t>{"Reference ID": "Q24851512"}</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -11236,7 +11384,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/c/c3/Abdullah_bin_Hamad_Al_Attiyah_2010.jpg</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/d/d7/Portrait_of_Ali_bin_Samikh_Al_Marri_at_the_Seventh_Abu_Dhabi_Dialogue_(ADD)_Ministerial_Consultation_in_Dubai.png</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
@@ -11247,7 +11395,7 @@
       <c r="T64" t="inlineStr"/>
       <c r="U64" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="V64" t="n">
@@ -11268,7 +11416,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>['1952-12-05']</t>
+          <t>['1972-11-30']</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
@@ -11278,12 +11426,12 @@
       </c>
       <c r="AD64" t="inlineStr">
         <is>
-          <t>['Also Known As', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name']</t>
+          <t>['Also Known As', 'Also Known As', 'Also Known As', 'Also Known As', 'Original Script Name']</t>
         </is>
       </c>
       <c r="AE64" t="inlineStr">
         <is>
-          <t>['Abdulla Bin Hamad Al Attiyah', 'عبد اللہ بن حمد العطیہ', 'อับดุลละห์ บิน ฮะมัด อัล อัตติยาห์', 'Abdallah Ben Hamad Al Attiyah', 'عبدالله بن حمد العطية', 'عبدالله بن حمد العطیه', 'Абдуллах бин Хамад Аль Аттиях', 'عبد الله بن حمد العطية', 'عبد اللَّه بن حمد العطية', '阿卜杜拉·本·哈马德·阿尔·阿蒂亚', 'Abdullah Bin Hamad Al Attiyah', 'アブドラ・ビン・ハマド・アル・アティヤ', '阿卜杜拉·本·哈馬德·艾爾·阿蒂亞']</t>
+          <t>['Ali Bin Samikh Al Marri', 'Ali Bin Saeed Bin Samikh Al Marri', 'He Dr Ali Bin Saeed Bin Smaikh Al Marri', 'Ali Bin Said Bin Smaikh Break Al Owair Al Marri', 'علي بن سعيد بن صميخ المرّي']</t>
         </is>
       </c>
       <c r="AF64" t="inlineStr">
@@ -11323,22 +11471,22 @@
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>['Politician']</t>
+          <t>['Academic', 'Minister', 'Official', 'Politician']</t>
         </is>
       </c>
       <c r="AN64" t="inlineStr">
         <is>
-          <t>['Deputy Prime Minister Of Qatar', 'Minister Of Industry And Energy', 'Minister Of Industry And Energy']</t>
+          <t>['Minister Of Labour']</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>['2007-04-03', '1992-03-28', '1999-01-12']</t>
+          <t>['2021-10-19']</t>
         </is>
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>['2011-01-18', '1995-02-19', '2011-01-18']</t>
+          <t>[None]</t>
         </is>
       </c>
       <c r="AQ64" t="inlineStr">
@@ -11360,7 +11508,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Abdulrahman Bin Hamad Al Attiyah</t>
+          <t>Abdullah Bin Hamad Al Attiyah</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
@@ -11371,7 +11519,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Qatari Diplomat And Former Secretary-General Of The Gulf Cooperation Council</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -11389,7 +11537,7 @@
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>{"Educated At": "University of Miami", "Reference ID": "Q307466"}</t>
+          <t>{"Educated At": "Alexandria University", "Reference ID": "Q2820939"}</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -11414,7 +11562,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/d/d2/Abdul_Rahman_bin_Hamad_Al_Attiyah.jpg</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/c/c3/Abdullah_bin_Hamad_Al_Attiyah_2010.jpg</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
@@ -11425,7 +11573,7 @@
       <c r="T65" t="inlineStr"/>
       <c r="U65" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="V65" t="n">
@@ -11446,7 +11594,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>['1950-04-15']</t>
+          <t>['1952-12-05']</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
@@ -11456,12 +11604,12 @@
       </c>
       <c r="AD65" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name']</t>
+          <t>['Also Known As', 'Original Script Name', 'Original Script Name', 'Also Known As']</t>
         </is>
       </c>
       <c r="AE65" t="inlineStr">
         <is>
-          <t>['عبد الرحمن بن حمد العطية', 'Abdul Rahman Bin Hamad Al Attiyah', '阿卜杜拉赫曼·本·哈马德·阿蒂亚', 'عبدالرحمن بن حمد العطیه', 'Abd Ar Rahman Ibn Hamad Al Attiyya', 'Abd Al Rahman Ibn Hamad Al Attiyya', 'عبد الرحمن العطية', 'Abdulrahman Bin Hamad Al Attiyah', 'Abdulrahman Bin Hamad El Attija', 'عبد الرحمن بن حمد العطيه', '阿卜杜拉赫曼·本·哈馬德·阿蒂亞', 'عبدالرحمن بن حمد العطية']</t>
+          <t>['Abdulla Bin Hamad Al Attiyah', 'عبد اللَّه بن حمد العطية', 'عبدالله بن حمد العطية', 'Abdallah Ben Hamad Al Attiyah']</t>
         </is>
       </c>
       <c r="AF65" t="inlineStr">
@@ -11501,22 +11649,22 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>['Diplomat', 'Politician']</t>
+          <t>['Politician']</t>
         </is>
       </c>
       <c r="AN65" t="inlineStr">
         <is>
-          <t>['Secretary-General Of The Gulf Cooperation Council']</t>
+          <t>['Deputy Prime Minister Of Qatar', 'Minister Of Industry And Energy', 'Minister Of Industry And Energy']</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>['2002-04-01']</t>
+          <t>['2007-04-03', '1992-03-28', '1999-01-12']</t>
         </is>
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>['2011-03-31']</t>
+          <t>['2011-01-18', '1995-02-19', '2011-01-18']</t>
         </is>
       </c>
       <c r="AQ65" t="inlineStr">
@@ -11538,14 +11686,10 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Abdullah Bin Khalifa Al Thani</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Khalifa Bin Hamad Al Thani</t>
-        </is>
-      </c>
+          <t>Abdulrahman Bin Hamad Al Attiyah</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
           <t>Male</t>
@@ -11553,7 +11697,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Prime Minister Of Qatar</t>
+          <t>Qatari Diplomat And Former Secretary-General Of The Gulf Cooperation Council</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -11571,7 +11715,7 @@
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>{"Educated At": "Royal Military Academy Sandhurst", "Reference ID": "Q317771"}</t>
+          <t>{"Educated At": "University of Miami", "Reference ID": "Q307466"}</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -11594,7 +11738,11 @@
           <t>Individual</t>
         </is>
       </c>
-      <c r="R66" t="inlineStr"/>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>https://upload.wikimedia.org/wikipedia/commons/d/d2/Abdul_Rahman_bin_Hamad_Al_Attiyah.jpg</t>
+        </is>
+      </c>
       <c r="S66" t="inlineStr">
         <is>
           <t>qa_gen</t>
@@ -11603,7 +11751,7 @@
       <c r="T66" t="inlineStr"/>
       <c r="U66" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="V66" t="n">
@@ -11624,7 +11772,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>['1958-02-11']</t>
+          <t>['1950-04-15']</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
@@ -11634,12 +11782,12 @@
       </c>
       <c r="AD66" t="inlineStr">
         <is>
-          <t>['Also Known As', 'Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Also Known As', 'Also Known As', 'Also Known As', 'Also Known As', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name', 'Also Known As', 'Also Known As', 'Also Known As']</t>
+          <t>['Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Also Known As', 'Also Known As', 'Also Known As']</t>
         </is>
       </c>
       <c r="AE66" t="inlineStr">
         <is>
-          <t>['Abdullah Bin Halife El Sani', 'アブドッラー・ビン・ハリーファ・アール＝サーニー', 'Abdallah Ibn Khalifah Al Thani', 'Abdallah Al Thani', 'عبدالله بن خليفه آل ثانی', 'Abdullah Ibn Khalifa Al Thani', 'Абд Аллах ібн Халіфа Аль Сані', 'Abdullah Bin Halife Al Sani', 'Abdullah Ibn Khalifah Al Thani', 'Abdullah Bin Khalifa Al Thani', 'Abdullah Bin Khalifah Al Thani', 'Abdulla Bin Nasser Bin Khalifa Al Thani', '阿卜杜拉·本·哈利法·阿勒薩尼', 'عبدالله بن خليفة آل ثاني', 'Abd Al·lah ibn Khalifa Al Thaní', '阿卜杜拉·本·哈利法·阿勒萨尼', 'Абдуллоҳ бин Халифа Оли Танӣ', 'Абдулла бин Халифа Аль Тани', "עבדאללה בן ח'ליפה אאל ת'אני", 'আব্দুল্লাহ বিন খলিফা আল থানি', 'Abdullah Ben Khalifa Al Thani', 'Абдула бин Халифа ал Тани', 'Sheik Abdullah Bin Khalifa Al Thani', 'Abdullah Bin Halife Es Sani', 'عبد الله بن خليفة آل ثاني', 'Abdullah Bin Chalifa Al Thani', 'Abdulla Bin Khalifa Al Thani', 'Abd Allah Ibn Chalifa Al Sani']</t>
+          <t>['عبد الرحمن بن حمد العطية', 'عبدالرحمن بن حمد العطية', 'عبد الرحمن بن حمد العطيه', 'Abd Al Rahman Ibn Hamad Al Attiyya', 'عبد الرحمن العطية', 'Abdulrahman Bin Hamad El Attija', 'Abd Ar Rahman Ibn Hamad Al Attiyya', 'Abdul Rahman Bin Hamad Al Attiyah']</t>
         </is>
       </c>
       <c r="AF66" t="inlineStr">
@@ -11679,32 +11827,32 @@
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>['Politician']</t>
+          <t>['Diplomat', 'Politician']</t>
         </is>
       </c>
       <c r="AN66" t="inlineStr">
         <is>
-          <t>['Prime Minister Of Qatar']</t>
+          <t>['Secretary-General Of The Gulf Cooperation Council']</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>['1996-10-29']</t>
+          <t>['2002-04-01']</t>
         </is>
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>['2007-04-03']</t>
+          <t>['2011-03-31']</t>
         </is>
       </c>
       <c r="AQ66" t="inlineStr">
         <is>
-          <t>['Sibling', 'Partner']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AR66" t="inlineStr">
         <is>
-          <t>['QA-GEN-HBKAT-0TKTJ-RCA-1', 'QA-GEN-LBJBH-RUAHV-RCA-1']</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -11716,10 +11864,14 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Abdullah Bin Khalid Al Thani</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr"/>
+          <t>Abdullah Bin Khalifa Al Thani</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Khalifa Bin Hamad Al Thani</t>
+        </is>
+      </c>
       <c r="D67" t="inlineStr">
         <is>
           <t>Male</t>
@@ -11727,10 +11879,14 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Former Minister Of The Interior Of Qatar</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr"/>
+          <t>Prime Minister Of Qatar</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Doha</t>
+        </is>
+      </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
@@ -11741,7 +11897,7 @@
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>{"Reference ID": "Q4666104"}</t>
+          <t>{"Educated At": "Royal Military Academy Sandhurst", "Reference ID": "Q317771"}</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -11773,7 +11929,7 @@
       <c r="T67" t="inlineStr"/>
       <c r="U67" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="V67" t="n">
@@ -11794,7 +11950,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>['1956-01-01']</t>
+          <t>['1958-02-11']</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
@@ -11804,12 +11960,12 @@
       </c>
       <c r="AD67" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As']</t>
+          <t>['Also Known As', 'Also Known As', 'Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name', 'Also Known As', 'Also Known As', 'Also Known As', 'Also Known As', 'Also Known As', 'Also Known As']</t>
         </is>
       </c>
       <c r="AE67" t="inlineStr">
         <is>
-          <t>['عبد الله بن خالد بن حمد آل ثاني', 'アブドュラー・ビン・カリド・アール＝サーニー', 'Абдулла бін Халід Аль Тані', 'アブドッラー・ビン・ハーリド・アール＝サーニー', 'عبدالله بن خالد بن حمد آل ثاني', 'عبد الله بن خالد آل ثاني', 'Абдулла бин Халид Аль Тани', 'Abdullah Bin Khalid Al Thani']</t>
+          <t>['Abdulla Bin Khalifa Al Thani', 'Abdullah Ibn Khalifah Al Thani', 'عبدالله بن خليفة آل ثاني', 'Abdullah Bin Khalifah Al Thani', 'Abdallah Al Thani', 'عبد الله بن خليفة آل ثاني', 'Abdullah Bin Chalifa Al Thani', 'Abdullah Bin Halife Al Sani', 'Abd Al·lah ibn Khalifa Al Thaní', 'Abd Allah Ibn Chalifa Al Sani', 'Abdullah Bin Halife Es Sani', 'Abdullah Bin Khalifa Al Thani', 'Abdallah Ibn Khalifah Al Thani', 'Abdulla Bin Nasser Bin Khalifa Al Thani', 'Sheik Abdullah Bin Khalifa Al Thani']</t>
         </is>
       </c>
       <c r="AF67" t="inlineStr">
@@ -11849,32 +12005,32 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Politician']</t>
         </is>
       </c>
       <c r="AN67" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Prime Minister Of Qatar']</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['1996-10-29']</t>
         </is>
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['2007-04-03']</t>
         </is>
       </c>
       <c r="AQ67" t="inlineStr">
         <is>
-          <t>['Child']</t>
+          <t>['Sibling', 'Partner']</t>
         </is>
       </c>
       <c r="AR67" t="inlineStr">
         <is>
-          <t>['QA-GEN-AAKHAT-U7E8Q-RCA-1']</t>
+          <t>['QA-GEN-HBKAT-0TKTJ-RCA-1', 'QA-GEN-LBJBH-RUAHV-RCA-1']</t>
         </is>
       </c>
     </row>
@@ -11886,7 +12042,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Abdullah Bin Nasser Bin Khalifa Al Thani</t>
+          <t>Abdullah Bin Khalid Al Thani</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
@@ -11897,14 +12053,10 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Qatari Politician</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Doha</t>
-        </is>
-      </c>
+          <t>Former Minister Of The Interior Of Qatar</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
         <v>0</v>
       </c>
@@ -11915,7 +12067,7 @@
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>{"Educated At": "Beirut Arab University", "Reference ID": "Q4666105"}</t>
+          <t>{"Reference ID": "Q4666104"}</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -11938,11 +12090,7 @@
           <t>Individual</t>
         </is>
       </c>
-      <c r="R68" t="inlineStr">
-        <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/8/8c/Sheikh_Abdullah_bin_Nasser_bin_Khalifa_Al_Thani.jpeg</t>
-        </is>
-      </c>
+      <c r="R68" t="inlineStr"/>
       <c r="S68" t="inlineStr">
         <is>
           <t>qa_gen</t>
@@ -11951,7 +12099,7 @@
       <c r="T68" t="inlineStr"/>
       <c r="U68" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="V68" t="n">
@@ -11972,7 +12120,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>['1960-01-01']</t>
+          <t>['1956-01-01']</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
@@ -11982,12 +12130,12 @@
       </c>
       <c r="AD68" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name']</t>
+          <t>['Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name']</t>
         </is>
       </c>
       <c r="AE68" t="inlineStr">
         <is>
-          <t>["עבדאללה בן נאסר בן ח'ליפה אאל ת'אני", 'عبد اللہ بن ناصر بن خلیفہ آل ثانی', 'Abdallah Ben Nasser Ben Khalifa Al Thani', 'Abdalla Nasirii filius Chalifae filii gentis Ṯānī', 'Abdullah Bin Nasir Al Sani', 'আবদুল্লাহ বিন নাসের বিন খলিফা আল থানি', 'アブドッラー・ビン・ナーセル・ビン・ハリーファ・アール＝サーニー', 'Абдулла бин Нассер бин Халифа Аль Тани', 'Abdullah Ibn Nasser Ibn Chalifa Al Thani', 'عبدالله بن ناصر بن خليفة آل ثاني', 'Абдуллоҳ бин Носир бин Халифа Оли Танӣ', 'عبدالله بن ناصر آل ثانی', 'Abdulla Bin Nasir Al Tani', "'Abd Allāh ibn Nāşir Āl Thānī", 'Abdullah bin Nasır es Sani', 'Abdullah Bin Nasser Bin Khalifa Al Thani', 'Αμπντάλα μπιν Νασέρ αλ Χαλίφα Αλ Θανί', '阿卜杜拉·本·纳赛尔·本·哈利法·阿勒萨尼', 'Абдулла бін Нассер бін Халіфа Аль Тані', 'Աբդուլա բին Նասեր բին Խալիֆա Ալ Տանի', 'عبد الله بن ناصر بن خليفة آل ثاني', 'Abd Allah Ibn Nasir Ibn Chalifa Al Sani', 'Abdullah bin Nasır Al Sani']</t>
+          <t>['Abdullah Bin Khalid Al Thani', 'アブドッラー・ビン・ハーリド・アール＝サーニー', 'عبدالله بن خالد بن حمد آل ثاني', 'عبد الله بن خالد آل ثاني']</t>
         </is>
       </c>
       <c r="AF68" t="inlineStr">
@@ -12027,32 +12175,32 @@
       </c>
       <c r="AM68" t="inlineStr">
         <is>
-          <t>['Politician']</t>
+          <t>['Diplomat', 'Politician']</t>
         </is>
       </c>
       <c r="AN68" t="inlineStr">
         <is>
-          <t>['Prime Minister Of Qatar']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>['2013-06-26']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>['2020-01-28']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AQ68" t="inlineStr">
         <is>
-          <t>['Relative']</t>
+          <t>['Child']</t>
         </is>
       </c>
       <c r="AR68" t="inlineStr">
         <is>
-          <t>['QA-GEN-HBKBAAT-ZM37Z-RCA-1']</t>
+          <t>['QA-GEN-AAKHAT-U7E8Q-RCA-1']</t>
         </is>
       </c>
     </row>
@@ -12064,7 +12212,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Salah Bin Ghanim Al Ali</t>
+          <t>Abdullah Bin Nasser Bin Khalifa Al Thani</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
@@ -12075,7 +12223,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Politician</t>
+          <t>Qatari Politician</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -12093,7 +12241,7 @@
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>{"Reference ID": "Q47490548"}</t>
+          <t>{"Educated At": "Beirut Arab University", "Reference ID": "Q4666105"}</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -12116,7 +12264,11 @@
           <t>Individual</t>
         </is>
       </c>
-      <c r="R69" t="inlineStr"/>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>https://upload.wikimedia.org/wikipedia/commons/8/8c/Sheikh_Abdullah_bin_Nasser_bin_Khalifa_Al_Thani.jpeg</t>
+        </is>
+      </c>
       <c r="S69" t="inlineStr">
         <is>
           <t>qa_gen</t>
@@ -12125,7 +12277,7 @@
       <c r="T69" t="inlineStr"/>
       <c r="U69" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="V69" t="n">
@@ -12146,7 +12298,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>['1966-08-03']</t>
+          <t>['1960-01-01']</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
@@ -12156,12 +12308,12 @@
       </c>
       <c r="AD69" t="inlineStr">
         <is>
-          <t>['Also Known As', 'Original Script Name', 'Original Script Name', 'Also Known As']</t>
+          <t>['Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name']</t>
         </is>
       </c>
       <c r="AE69" t="inlineStr">
         <is>
-          <t>['Salah Bin Ghanem Al Ali', 'صلاح بن غانم العلی', 'صلاح بن غانم العلي', 'Salah Bin Ghanim Al Ali']</t>
+          <t>['عبد الله بن ناصر بن خليفة آل ثاني', 'Abdullah bin Nasır Al Sani', 'عبدالله بن ناصر بن خليفة آل ثاني', 'Abd Allah Ibn Nasir Ibn Chalifa Al Sani', 'Abdallah Ben Nasser Ben Khalifa Al Thani', 'Abdullah bin Nasır es Sani']</t>
         </is>
       </c>
       <c r="AF69" t="inlineStr">
@@ -12206,27 +12358,27 @@
       </c>
       <c r="AN69" t="inlineStr">
         <is>
-          <t>['Minister Of Sports And Youth']</t>
+          <t>['Prime Minister Of Qatar']</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>['2021-10-19']</t>
+          <t>['2013-06-26']</t>
         </is>
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>[None]</t>
+          <t>['2020-01-28']</t>
         </is>
       </c>
       <c r="AQ69" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Relative']</t>
         </is>
       </c>
       <c r="AR69" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['QA-GEN-HBKBAAT-ZM37Z-RCA-1']</t>
         </is>
       </c>
     </row>
@@ -12238,7 +12390,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Nassir Abdulaziz Al Nasser</t>
+          <t>Salah Bin Ghanim Al Ali</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
@@ -12249,7 +12401,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>President Of The United Nations General Assembly</t>
+          <t>Politician</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -12267,7 +12419,7 @@
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
-          <t>{"Educated At": "Beirut Arab University", "Reference ID": "Q529388"}</t>
+          <t>{"Reference ID": "Q47490548"}</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -12290,11 +12442,7 @@
           <t>Individual</t>
         </is>
       </c>
-      <c r="R70" t="inlineStr">
-        <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/d/d4/Nassir_Abdulaziz_Al-Nasser.jpg</t>
-        </is>
-      </c>
+      <c r="R70" t="inlineStr"/>
       <c r="S70" t="inlineStr">
         <is>
           <t>qa_gen</t>
@@ -12303,7 +12451,7 @@
       <c r="T70" t="inlineStr"/>
       <c r="U70" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="V70" t="n">
@@ -12324,7 +12472,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>['1952-09-15']</t>
+          <t>['1966-08-03']</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
@@ -12334,12 +12482,12 @@
       </c>
       <c r="AD70" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name']</t>
+          <t>['Also Known As', 'Also Known As', 'Original Script Name']</t>
         </is>
       </c>
       <c r="AE70" t="inlineStr">
         <is>
-          <t>['ナーセル・アルナセル', 'ناصر عبد العزيز الناصر', 'Nassir Abdulaziz Al Nasser', 'ناصر عبدالعزیز النصر', '納赛尔', 'Nassir Abdulasis An Nasser', 'Nasser Bin Abdulaziz El Nasr', 'Nassir Abd al ʿAzīz an Nasser', 'ナーセル・アブドゥラジズ・アルナセル', '納賽爾', 'Nassir Al Nasser', 'Nāṣir ibn ʿAbd al ʿAzīz al Naṣr']</t>
+          <t>['Salah Bin Ghanem Al Ali', 'Salah Bin Ghanim Al Ali', 'صلاح بن غانم العلي']</t>
         </is>
       </c>
       <c r="AF70" t="inlineStr">
@@ -12379,22 +12527,22 @@
       </c>
       <c r="AM70" t="inlineStr">
         <is>
-          <t>['Diplomat', 'Politician']</t>
+          <t>['Politician']</t>
         </is>
       </c>
       <c r="AN70" t="inlineStr">
         <is>
-          <t>['President Of The United Nations General Assembly', 'Ambassador Of Qatar To Jordan']</t>
+          <t>['Minister Of Sports And Youth']</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['2021-10-19']</t>
         </is>
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[None]</t>
         </is>
       </c>
       <c r="AQ70" t="inlineStr">
@@ -12416,7 +12564,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Ali Bin Fetais Al Marri</t>
+          <t>Nassir Abdulaziz Al Nasser</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
@@ -12427,7 +12575,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Qatari Lawyer</t>
+          <t>President Of The United Nations General Assembly</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -12445,7 +12593,7 @@
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
-          <t>{"Educated At": "Sorbonne University, University of Rennes", "Reference ID": "Q55081149"}</t>
+          <t>{"Educated At": "Beirut Arab University", "Reference ID": "Q529388"}</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -12470,7 +12618,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/8/8b/Dr._Ali_Bin_Fetais_Al_Marri.jpg</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/d/d4/Nassir_Abdulaziz_Al-Nasser.jpg</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
@@ -12481,7 +12629,7 @@
       <c r="T71" t="inlineStr"/>
       <c r="U71" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="V71" t="n">
@@ -12502,7 +12650,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>['1965-02-08']</t>
+          <t>['1952-09-15']</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
@@ -12512,12 +12660,12 @@
       </c>
       <c r="AD71" t="inlineStr">
         <is>
-          <t>['Also Known As', 'Also Known As', 'Original Script Name', 'Also Known As', 'Original Script Name']</t>
+          <t>['Also Known As', 'Also Known As', 'Also Known As', 'Original Script Name', 'Original Script Name']</t>
         </is>
       </c>
       <c r="AE71" t="inlineStr">
         <is>
-          <t>['Ali Bin Fetais Al Marri', 'Ali Bin Mohsen Bin Fetais Al Marri', 'على بن فطيس المرى', 'Ali Bin Feitais Al Marri', 'علي بن فطيس المري']</t>
+          <t>['Nassir Abdulasis An Nasser', 'Nassir Abdulaziz Al Nasser', 'Nasser Bin Abdulaziz El Nasr', "['Nassir Abd al ʿAzīz an Nasser']", 'ナーセル・アブドゥラジズ・アルナセル']</t>
         </is>
       </c>
       <c r="AF71" t="inlineStr">
@@ -12557,12 +12705,12 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Diplomat', 'Politician']</t>
         </is>
       </c>
       <c r="AN71" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['President Of The United Nations General Assembly', 'Ambassador Of Qatar To Jordan']</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
@@ -12594,14 +12742,10 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Hamad Bin Khalifa Al Thani</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Khalifa Bin Hamad Al Thani</t>
-        </is>
-      </c>
+          <t>Ali Bin Fetais Al Marri</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
           <t>Male</t>
@@ -12609,7 +12753,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Emir Of Qatar From 1995 To 2013</t>
+          <t>Qatari Lawyer</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -12627,7 +12771,7 @@
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
-          <t>{"Educated At": "Royal Military Academy Sandhurst", "Reference ID": "Q57360"}</t>
+          <t>{"Educated At": "Sorbonne University, University of Rennes", "Reference ID": "Q55081149"}</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -12652,7 +12796,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/a/a6/5th_Global_Forum_Vienna_2013_(8512954534)_(cropped).jpg</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/8/8b/Dr._Ali_Bin_Fetais_Al_Marri.jpg</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
@@ -12663,7 +12807,7 @@
       <c r="T72" t="inlineStr"/>
       <c r="U72" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="V72" t="n">
@@ -12684,7 +12828,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>['1952-01-01']</t>
+          <t>['1965-02-08']</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
@@ -12694,12 +12838,12 @@
       </c>
       <c r="AD72" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Also Known As', 'Also Known As', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name']</t>
+          <t>['Also Known As', 'Also Known As']</t>
         </is>
       </c>
       <c r="AE72" t="inlineStr">
         <is>
-          <t>['حمد بن خلیفه آلثانی', 'Hàmad ibn Khalifa Al Thani', 'Hamad Bin Khalifa Bin Hamad Bin Abdullah Bin Jassim Bin Mohammed Al Thani', 'Hamad Bin Khalifa Bin Hamad Bin Abdullah Bin Dschasim Bin Muhammed Al Thani', 'Хамад бин Халифа ал Тани', 'Hamidus Chalifae filius gentis Ṯānī', 'ハマド・ビン・ハリーファ・アール＝サーニー', 'Hamad Ál Thání', 'حمد بن خلیفہ آل ثانی', 'Hamad Ibn Chalifa', 'Hamid Bin Halife El Sani', 'சேக் அமத் பின் கலீபா அல் தானி', 'Hamad bin Chalífa', '哈马德·本·哈利法·阿勒萨尼', 'Mohammed Bin Hamad Bin Khalifa Al Thani', 'Hamad bin Chalífa Ál Thání', 'Hamad Bin Khalifa Al Tsani', 'Համադ բին Խալիֆա ալ Թանի', 'Hamad Bin Chalifa', 'हमद बिन खलीफा अल थानी', 'Sheikh Hamad Bin Khalifa Al Tsani', 'حمد بن خلیفهٔ آلثانی', '哈迈德·本·哈利法·阿勒萨尼', 'เชคฮามัด บิน คอลีฟะห์ อัลตานี', 'ഹമദ് ബിൻ ഖലീഫ അൽതാനി', 'Hamad Bin Halifa Al Tani', 'Hamad Ben Khalifa Al Thani', 'Hamad ibn Halífa Ál Táni', 'Hamad Ibn Chalifa Al Sani', 'シェイク・ハマド・ビン・ハリーファ・アール・サーニ', 'Hamad Bin Halifa', 'Hamad Bin Kalifa Al Tani', 'حمد بن خلیفه آل ثانی', '셰이크 하마드 이븐 할리파 알 타니', 'Hamad Bin Khalifa', 'Hamad bin Ĥalifa Al Thani', 'Hamadas Bin Chalifa', 'হামাদ বিন খলিফা আল থানী', 'Хамад ибн Халифа аль Тани', 'حمد بن خلیفہ الثانی', '하마드 빈 칼리파 알사니', 'Hamad Al Tani', 'Hamads bin Halīfa', 'Хамад бин Халифа аль Сани', 'حمد بن خليفة', 'Ḩamad ibn Khalīfah Āl Thānī', 'Хамад бин Халифа аль Тани', 'Hamad Bin Khalifa Al Thani', 'ハマド・ビン・ハリーファ・アル＝サーニ', 'Hammad Al Thani', 'হামাদ বিন খলিফা আল থানি', 'Hamad Bin Xəlifə Al Tani', 'Хамад бин Халифа ат Тани', "חמד בן ח'ליפה אאל ת'אני", 'Хамад бин Халифа аc Cани', 'Hamad Ibn Khalifah Al Thani', 'الشيخ حمد بن خليفة آل ثاني', 'حمد بن خلیفه آل دوم', 'Χαμάντ μπιν Χαλίφα', 'Mohammed Bin Khalifa Al Thani', 'Hamad Bin Jalifa Al Thani', 'Hamad Ibn Khalifa', 'Hamads Bin Halifa', 'เอมีร์เชคฮามัด บิน คอลีฟะห์ อัลตานี', 'Ҳамад бин Халифа Оли Танӣ', 'حمد بن خلیفه الثانی', 'Hamad Bin Halife Es Sani', 'Sheikh Hamad Bin Khalifa Al Thani', 'حمد بن خليفة ال ثاني', 'Hamad Ibn Khalifa Al Thani', 'ฮะมัด บิน เคาะลีฟะฮ์ อาล ษานี', 'Hamad Khalifa Bin Al Thani', 'حمد بن خليفة ال ثانى', 'Hamad Bin Khalifa Al Tani', 'Σεΐχης Χαμάντ ιμπν Χαλίφα αλ Θανί', 'Гамад бін Халіфа аль Тані', '하마드 빈 할리파 알 사니', 'Hammad Bin Khalifa Al Thani', '하마드 빈 칼리파', 'Hamad Al Thani', 'Hamadas Bin Chalifa Al Tanis', 'حمد بن خلیفه ال دوم', 'حمد بن خلیفهٔ آل دوم', '하마드 빈 할리파', '하마드 빈 할리파 알사니', 'ჰამად ბინ ხალიფა ალ თანი', 'حمد بن خلیفهٔ ال ثانی', 'Хамад бин Халифа Аль Тани', 'Хамад бин Халифа', 'Хамад бін Халіфа Аль Тані', 'Khalifa Hamad Bin', 'حمد بن خليفة آل ثاني', 'Χαμάντ μπιν Χαλίφα αλ Θανί', 'Cheikh Hamad Ben Khalifa Al Thani', 'Hamád Ibn Chalífa as Sání', 'حمد بن خليفه آل ثاني', 'Hamed Bin Halife El Sani', 'Hamad bin Khalifa   حمد بن خليفة ال ثاني', 'Σεΐχης Χαμάντ μπιν Χαλίφα', 'حمد بن خلیفه ال ثانی', 'Хамад Бин Халифа', 'Həməd ibn Xəlifə Ali Sani', 'Hamad Bin Chalifa Al Thani', 'Hameds bin Halīfa al Tānī', "חמד בן ח'ליפה", 'حمد بن خلیفهٔ آل ثانی', 'حمد آل ثاني']</t>
+          <t>['Ali Bin Fetais Al Marri', 'Ali Bin Mohsen Bin Fetais Al Marri']</t>
         </is>
       </c>
       <c r="AF72" t="inlineStr">
@@ -12739,32 +12883,32 @@
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>['Politician']</t>
+          <t>['Civil Servant', 'Executive Director', 'Lawyer', 'Politician', 'University Teacher']</t>
         </is>
       </c>
       <c r="AN72" t="inlineStr">
         <is>
-          <t>['Emir Of The State Of Qatar']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>['1995-06-26']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>['2013-06-25']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AQ72" t="inlineStr">
         <is>
-          <t>['Sibling', 'Sibling', 'Sibling', 'Partner', 'Relative', 'Relative', 'Child', 'Child', 'Child', 'Child', 'Child', 'Child', 'Child', 'Child', 'Child', 'Child', 'Child', 'Child']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AR72" t="inlineStr">
         <is>
-          <t>['QA-GEN-ABKAT-KXNJ5-RCA-1', 'QA-GEN-ABKAT-7QHEU-RCA-1', 'QA-GEN-MBKAT-TDAMF-RCA-1', 'QA-GEN-MBNAM-IN51I-RCA-1', 'QA-GEN-HBSAT-LEUBZ-RCA-1', 'QA-GEN-SBHAT-GX4H3-RCA-1', 'QA-GEN-ABHBKAT-87DYX-RCA-1', 'QA-GEN-KBHAT-OL3FU-RCA-1', 'QA-GEN-MBHBKAT-XHR18-RCA-1', 'QA-GEN-MBHBKAT-LRHZY-RCA-1', 'QA-GEN-MBHBKAT-C3NWO-RCA-1', 'QA-GEN-PJBHOQ-PNKIK-RCA-1', 'QA-GEN-PJBHOQ-B78MR-RCA-1', 'QA-GEN-PKBHOQ-B6NQQ-RCA-1', 'QA-GEN-PAMBHOQ-3MSTL-RCA-1', 'QA-GEN-PHBHOQ-MJ0UC-RCA-1', 'QA-GEN-TBHA-K036O-RCA-1', 'QA-GEN-TBHAT-28KU2-RCA-1']</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -12776,18 +12920,22 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Hessa Al Jaber</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr"/>
+          <t>Hamad Bin Khalifa Al Thani</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Khalifa Bin Hamad Al Thani</t>
+        </is>
+      </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Qatari Engineer And Politician</t>
+          <t>Emir Of Qatar From 1995 To 2013</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -12805,7 +12953,7 @@
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
-          <t>{"Educated At": "George Washington University, Kuwait University", "Reference ID": "Q5746141"}</t>
+          <t>{"Educated At": "Royal Military Academy Sandhurst", "Reference ID": "Q57360"}</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -12830,7 +12978,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/e/ee/Dr.Hessa-Al-Jaber2014.png</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/a/a6/5th_Global_Forum_Vienna_2013_(8512954534)_(cropped).jpg</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
@@ -12841,7 +12989,7 @@
       <c r="T73" t="inlineStr"/>
       <c r="U73" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="V73" t="n">
@@ -12862,7 +13010,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>['1959-01-01']</t>
+          <t>['1952-01-01']</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
@@ -12872,12 +13020,12 @@
       </c>
       <c r="AD73" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name']</t>
+          <t>['Also Known As', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name', 'Also Known As', 'Also Known As', 'Also Known As', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Also Known As', 'Also Known As', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name']</t>
         </is>
       </c>
       <c r="AE73" t="inlineStr">
         <is>
-          <t>["חיסה אל ג'אבר", 'Hessa Al Jaber', 'Hessa Bint Sultan Al Jaber', 'হেসা আল জাবের', 'حصه الجابر', 'Hessa Sultan Jaber Mohamed Al Jaber', 'Hessa Sultan Al Jaber', 'حصة الجابر']</t>
+          <t>['Hamad Bin Chalifa Al Thani', '哈迈德·本·哈利法·阿勒萨尼', 'Хамад бин Халифа аль Тани', 'Hamad Bin Jalifa Al Thani', 'حمد بن خليفة', 'Hamad Ben Khalifa Al Thani', 'حمد بن خلیفه ال ثانی', 'ハマド・ビン・ハリーファ・アル＝サーニ', '하마드 빈 칼리파', 'Sheikh Hamad Bin Khalifa Al Thani', 'Σεΐχης Χαμάντ μπιν Χαλίφα', 'Hamad Ál Thání', 'Хамад бин Халифа ат Тани', 'Hamad Bin Khalifa Bin Hamad Bin Abdullah Bin Dschasim Bin Muhammed Al Thani', 'الشيخ حمد بن خليفة آل ثاني', 'حمد آل ثاني', 'Hamads Bin Halifa', 'حمد بن خليفه آل ثاني', 'Hammad Bin Khalifa Al Thani', 'حمد بن خلیفه الثانی', 'حمد بن خلیفهٔ آل ثانی', 'เชคฮามัด บิน คอลีฟะห์ อัลตานี', '하마드 빈 할리파', '하마드 빈 할리파 알 사니', 'Hamad Bin Khalifa Bin Hamad Bin Abdullah Bin Jassim Bin Mohammed Al Thani', 'Hamid Bin Halife El Sani', "חמד בן ח'ליפה", 'Hamad Khalifa Bin Al Thani', 'Hammad Al Thani', 'Cheikh Hamad Ben Khalifa Al Thani', 'حمد بن خلیفه آلثانی', 'Hamad Ibn Khalifah Al Thani', 'حمد بن خلیفهٔ آل دوم', 'Hamad Bin Khalifa Al Thani', 'Həməd ibn Xəlifə Ali Sani', 'Mohammed Bin Hamad Bin Khalifa Al Thani', 'Hamads bin Halīfa', 'Хамад ибн Халифа аль Тани', 'Hamad Al Tani', 'Hamadas Bin Chalifa', 'حمد بن خلیفه ال دوم', 'Khalifa Hamad Bin', 'Hamad Bin Chalifa', 'Хамад бин Халифа аль Сани', 'Хамад бин Халифа', 'Hamad Bin Kalifa Al Tani', 'Hamád Ibn Chalífa as Sání', 'Σεΐχης Χαμάντ ιμπν Χαλίφα αλ Θανί', 'حمد بن خليفة آل ثاني', 'Hamad bin Khalifa   حمد بن خليفة ال ثاني', 'Hamad Ibn Chalifa', 'シェイク・ハマド・ビン・ハリーファ・アール・サーニ', 'حمد بن خليفة ال ثاني', 'Hamad Bin Halifa', 'Hamad Al Thani', 'Χαμάντ μπιν Χαλίφα', 'Hamad Ibn Khalifa Al Thani', 'Hamad Ibn Khalifa', 'Хамад бин Халифа аc Cани', 'Hamad bin Chalífa', '셰이크 하마드 이븐 할리파 알 타니', '하마드 빈 칼리파 알사니', 'حمد بن خلیفهٔ ال ثانی', 'เอมีร์เชคฮามัด บิน คอลีฟะห์ อัลตานี', 'Mohammed Bin Khalifa Al Thani', 'Hamad Bin Khalifa', 'Sheikh Hamad Bin Khalifa Al Tsani', 'Hamed Bin Halife El Sani', 'حمد بن خلیفه آل دوم', 'Hàmad ibn Khalifa Al Thani', 'حمد بن خلیفهٔ آلثانی']</t>
         </is>
       </c>
       <c r="AF73" t="inlineStr">
@@ -12917,32 +13065,32 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Politician']</t>
         </is>
       </c>
       <c r="AN73" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Emir Of The State Of Qatar']</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['1995-06-26']</t>
         </is>
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['2013-06-25']</t>
         </is>
       </c>
       <c r="AQ73" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Child', 'Child', 'Child', 'Child', 'Child', 'Child', 'Child', 'Child', 'Child', 'Child', 'Child', 'Child', 'Sibling', 'Sibling', 'Sibling', 'Relative', 'Relative', 'Partner']</t>
         </is>
       </c>
       <c r="AR73" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['QA-GEN-ABHBKAT-87DYX-RCA-1', 'QA-GEN-KBHAT-OL3FU-RCA-1', 'QA-GEN-MBHBKAT-XHR18-RCA-1', 'QA-GEN-MBHBKAT-LRHZY-RCA-1', 'QA-GEN-MBHBKAT-C3NWO-RCA-1', 'QA-GEN-PJBHOQ-PNKIK-RCA-1', 'QA-GEN-PJBHOQ-B78MR-RCA-1', 'QA-GEN-PKBHOQ-B6NQQ-RCA-1', 'QA-GEN-PAMBHOQ-3MSTL-RCA-1', 'QA-GEN-PHBHOQ-MJ0UC-RCA-1', 'QA-GEN-TBHA-K036O-RCA-1', 'QA-GEN-TBHAT-28KU2-RCA-1', 'QA-GEN-ABKAT-KXNJ5-RCA-1', 'QA-GEN-ABKAT-7QHEU-RCA-1', 'QA-GEN-MBKAT-4O4S5-RCA-1', 'QA-GEN-HBSAT-LEUBZ-RCA-1', 'QA-GEN-SBHAT-GX4H3-RCA-1', 'QA-GEN-MBNAM-IN51I-RCA-1']</t>
         </is>
       </c>
     </row>
@@ -12954,18 +13102,18 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Hamad Bin Jassim Bin Jaber Al Thani</t>
+          <t>Hessa Al Jaber</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Qatari Politician; Prime Minister And Foreign Minister</t>
+          <t>Qatari Engineer And Politician</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -12983,7 +13131,7 @@
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
-          <t>{"Educated At": "Cairo University", "Reference ID": "Q57734"}</t>
+          <t>{"Educated At": "George Washington University, Kuwait University", "Reference ID": "Q5746141"}</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -13008,7 +13156,7 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/6/6f/Hamad_Bin_Jassim.png</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/e/ee/Dr.Hessa-Al-Jaber2014.png</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
@@ -13019,7 +13167,7 @@
       <c r="T74" t="inlineStr"/>
       <c r="U74" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="V74" t="n">
@@ -13040,7 +13188,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>['1959-08-30']</t>
+          <t>['1959-01-01']</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
@@ -13050,12 +13198,12 @@
       </c>
       <c r="AD74" t="inlineStr">
         <is>
-          <t>['Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Also Known As', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name']</t>
+          <t>['Also Known As', 'Also Known As', 'Also Known As', 'Also Known As']</t>
         </is>
       </c>
       <c r="AE74" t="inlineStr">
         <is>
-          <t>['Hamad Bin Jassem Bin Jaber Al Thani', 'حمد بن جاسم ال ثاني', 'Хамид бен Джасим бен Джабер аль Тани', '하마드 빈 자심 빈 자베르 알사니', 'Համադ Բեն Ջասիմ Բեն Ջաբերեր Ալ Թանի', 'Hamad Ibn Jaber Al Thani', 'Хамад бин Джабер Аль Тани', 'হামাদ বিন জসিম বিন জাবের আল থানি', 'Хамад бин Джабер аль Тани', 'Hamad Ben Jassim Ben Jaber Al Thani', 'হামাদ বিন জাছিম বিন জাবৰ আল থানী', 'H E Sheikh Hamad Bin Jassim Bin Jabr Al Thani', 'Hamad Ibn Jabir Al Thani', 'हमद बिन जसीम बिन जबर अल थानी', 'الشيخ حمد بن جاسم بن جبر آل ثاني', 'ハマド・ビン・ジャーシム・ビン・ジャブル・アール＝サーニー', 'حمد بن جاسم آل ثاني', 'Hamad Ibn Jassim Ibn Jabr As Sani', 'Хамад бін Джасім бін Джабер Аль Тані', 'Hamad Bin Jassim Al Thani', 'حمد بن جاسم بن جبر آل ثاني', 'Σεΐχης Χαμάντ ιμπν Τζαμπρ αλ Θανί', 'Χαμάντ μπιν Τζασίμ μπιν Τζαμπίρ αλ Θανί', 'Hamadas bin Džasimas bin Džaberas al Tanis', 'Хамад бен Џабер ел Тани', 'Ҳамад бин Ҷосим бин Ҷобир Оли Танӣ', 'Хамад Бин Џабер ел Тани', 'Sheikh Hamad Ibn Jaber Al Thani', '哈马德·本·贾西姆·阿勒萨尼', 'Hamad Bin Jassem Bin Jabr Al Thani', 'Hamad Ibn Jassim Ibn Jaber Al Thani', 'ハマド・ビン・ジャシム', 'Hamad bin Dzsászim bin Dzsaber esz Szání', "חמד בן ג'אסם בן ג'אבר אאל ת'אני", 'حمد بن جاسم بن جبر ال تانى', 'Hamad Ibn Jassim Al Thani', 'Ḩamad ibn Jābir Āl Thānī', 'حمد بن جاسم بن جبر ال دوم', 'حمد بن جاسم بن جبر آل ثانی', 'Hamad Ibn Dschasim Ibn Dschabr Al Thani', 'Χαμάντ μπιν Τζασίμ μπιν Τζαμπέρ Αλ Θανί', 'حمد بن جاسم بن جبر ال ثانی', '哈马德·本·贾西姆·本·贾比尔·阿勒萨尼', 'Хамад Бин Џабер ал Тани', 'Hamad Bin Jassim Bin Jaber Al Thani', 'Hamad Ben Jassim Al Thani', 'Hamad Bin Dschassim Bin Dschaber Al Thani', 'Hamad ibn Dżassim ibn Dżabr Al Sani', 'حمد بن جاسم بن جبر آل دوم', 'Hamad Bin Casim Bin Cabir El Tani', 'Hamad Bin Casim Bin Cabir Es Sani', 'حماد بن جاسم بن جبر الثانی']</t>
+          <t>['Hessa Bint Sultan Al Jaber', 'Hessa Sultan Jaber Mohamed Al Jaber', 'Hessa Sultan Al Jaber', 'Hessa Al Jaber']</t>
         </is>
       </c>
       <c r="AF74" t="inlineStr">
@@ -13095,22 +13243,22 @@
       </c>
       <c r="AM74" t="inlineStr">
         <is>
-          <t>['Diplomat', 'Politician']</t>
+          <t>['Engineer', 'Politician']</t>
         </is>
       </c>
       <c r="AN74" t="inlineStr">
         <is>
-          <t>['Minister Of Agriculture', 'Minister Of Foreign Affairs Of Qatar', 'Prime Minister Of Qatar']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>['1989-01-01', '1992-01-11', '2007-04-03']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>['1990-01-01', '2013-06-25', '2013-06-26']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AQ74" t="inlineStr">
@@ -13132,7 +13280,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Jassim Bin Saif Al Sulaiti</t>
+          <t>Hamad Bin Jassim Bin Jaber Al Thani</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
@@ -13141,8 +13289,16 @@
           <t>Male</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Qatari Politician; Prime Minister And Foreign Minister</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Doha</t>
+        </is>
+      </c>
       <c r="G75" t="n">
         <v>0</v>
       </c>
@@ -13153,7 +13309,7 @@
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
-          <t>{"Reference ID": "Q59221582"}</t>
+          <t>{"Educated At": "Cairo University", "Reference ID": "Q57734"}</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -13178,7 +13334,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/c/c1/Jassim_Bin_Saif_Al_Sulaiti_-_2018_(cropped).jpg</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/6/6f/Hamad_Bin_Jassim.png</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
@@ -13189,7 +13345,7 @@
       <c r="T75" t="inlineStr"/>
       <c r="U75" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="V75" t="n">
@@ -13210,22 +13366,22 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['1959-08-30']</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Qatar']</t>
         </is>
       </c>
       <c r="AD75" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Also Known As']</t>
+          <t>['Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Also Known As', 'Also Known As', 'Also Known As', 'Original Script Name', 'Also Known As', 'Also Known As', 'Also Known As', 'Also Known As', 'Also Known As', 'Original Script Name', 'Also Known As', 'Original Script Name']</t>
         </is>
       </c>
       <c r="AE75" t="inlineStr">
         <is>
-          <t>['جاسم بن سيف السليطي', 'Jassim Bin Saif Al Sulaiti']</t>
+          <t>['Χαμάντ μπιν Τζασίμ μπιν Τζαμπίρ αλ Θανί', 'Χαμάντ μπιν Τζασίμ μπιν Τζαμπέρ Αλ Θανί', 'Хамад Бин Џабер ел Тани', 'حمد بن جاسم ال ثاني', 'Hamad Bin Jassim Bin Jaber Al Thani', 'حمد بن جاسم بن جبر ال ثانی', 'Хамад бин Джабер аль Тани', 'ハマド・ビン・ジャシム', 'Hamad Ben Jassim Ben Jaber Al Thani', 'حمد بن جاسم آل ثاني', 'Хамад Бин Џабер ал Тани', '哈马德·本·贾西姆·阿勒萨尼', 'Хамид бен Джасим бен Джабер аль Тани', 'Hamad Ibn Jaber Al Thani', 'H E Sheikh Hamad Bin Jassim Bin Jabr Al Thani', 'Hamad Bin Jassem Bin Jaber Al Thani', 'Hamad Ibn Jassim Ibn Jabr As Sani', 'حمد بن جاسم بن جبر ال دوم', 'Hamad Ben Jassim Al Thani', 'Hamad Bin Dschassim Bin Dschaber Al Thani', 'Hamad Bin Casim Bin Cabir Es Sani', 'Hamad Ibn Jabir Al Thani', 'Hamad Bin Jassim Al Thani', 'حمد بن جاسم بن جبر آل دوم', 'Sheikh Hamad Ibn Jaber Al Thani', 'الشيخ حمد بن جاسم بن جبر آل ثاني']</t>
         </is>
       </c>
       <c r="AF75" t="inlineStr">
@@ -13265,22 +13421,22 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Diplomat', 'Politician']</t>
         </is>
       </c>
       <c r="AN75" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Minister Of Agriculture', 'Minister Of Foreign Affairs Of Qatar', 'Prime Minister Of Qatar']</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['1989-01-01', '1992-01-11', '2007-04-03']</t>
         </is>
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['1990-01-01', '2013-06-25', '2013-06-26']</t>
         </is>
       </c>
       <c r="AQ75" t="inlineStr">
@@ -13302,14 +13458,10 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Prince Jassim Bin Hamad Of Qatar</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Hamad Bin Khalifa Al Thani</t>
-        </is>
-      </c>
+          <t>Jassim Bin Saif Al Sulaiti</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
           <t>Male</t>
@@ -13317,14 +13469,10 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Qatari Royal</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Doha</t>
-        </is>
-      </c>
+          <t>Qatari Politician</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
         <v>0</v>
       </c>
@@ -13335,7 +13483,7 @@
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr">
         <is>
-          <t>{"Educated At": "Royal Military Academy Sandhurst", "Reference ID": "Q6161563"}</t>
+          <t>{"Reference ID": "Q59221582"}</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -13360,7 +13508,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/4/46/Jassim_bin_Hamad_bin_Khalifa_Al_Thani.jpg</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/c/c1/Jassim_Bin_Saif_Al_Sulaiti_-_2018_(cropped).jpg</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
@@ -13371,7 +13519,7 @@
       <c r="T76" t="inlineStr"/>
       <c r="U76" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="V76" t="n">
@@ -13392,7 +13540,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>['1978-08-25']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
@@ -13402,12 +13550,12 @@
       </c>
       <c r="AD76" t="inlineStr">
         <is>
-          <t>['Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Also Known As', 'Also Known As', 'Original Script Name']</t>
+          <t>['Also Known As', 'Also Known As']</t>
         </is>
       </c>
       <c r="AE76" t="inlineStr">
         <is>
-          <t>['Jasim Bin Hamad Bin Khalifa Al Thani', 'جاسم بن حمد آل ثاني', 'جاسم بن حمد بن خليفة آل ثاني', '賈辛·本·哈邁德·本·哈利法·阿勒薩尼', 'Джасим бин Хамад бин Халифа Аль Тани', 'Jàssim ibn Hàmad ibn Khalifa Al Thani', 'جاسم بن حمد بن خلیفه آل ثانی', "ג'אסם בן חמד בן ח'ליפה אאל ת'אני", 'জসিম বিন হামাদ বিন খলিফা আল থানি', 'Jassim Bin Hamad Al Thani', 'Jassim Bin Hamad Bin Khalifa Al Thani', 'ジャーシム', '贾西姆·本·哈马德·本·哈利法·阿勒萨尼', 'Dżasim ibn Hamad ibn Chalifa Al Sani', 'ジャーシム・ビン・ハマド・アール＝サーニー', 'Prinz Jassim Bin Hamad Von Katar', 'Jasmin Bin Hamad Bin Khalifa Al Thani', 'Jasim Bin Hamad Al Thani', 'Dzsászim bin Hamad bin Halífa ál Szání']</t>
+          <t>['Jassim Bin Saif Ahmed Al Sulaiti', 'Jassim Bin Saif Al Sulaiti']</t>
         </is>
       </c>
       <c r="AF76" t="inlineStr">
@@ -13447,7 +13595,7 @@
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Politician']</t>
         </is>
       </c>
       <c r="AN76" t="inlineStr">
@@ -13467,12 +13615,12 @@
       </c>
       <c r="AQ76" t="inlineStr">
         <is>
-          <t>['Sibling', 'Sibling', 'Sibling', 'Sibling', 'Sibling', 'Sibling', 'Sibling', 'Sibling', 'Sibling', 'Sibling', 'Partner', 'Mother']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AR76" t="inlineStr">
         <is>
-          <t>['QA-GEN-ABHBKAT-87DYX-RCA-1', 'QA-GEN-KBHBKAT-A7NJG-RCA-1', 'QA-GEN-MBHBKAT-XHR18-RCA-1', 'QA-GEN-MBHBKAT-LRHZY-RCA-1', 'QA-GEN-MBHBKAT-C3NWO-RCA-1', 'QA-GEN-PJBHOQ-B78MR-RCA-1', 'QA-GEN-PKBHOQ-B6NQQ-RCA-1', 'QA-GEN-PAMBHOQ-3MSTL-RCA-1', 'QA-GEN-PHBHOQ-MJ0UC-RCA-1', 'QA-GEN-TBHA-K036O-RCA-1', 'QA-GEN-BBHAT-FD404-RCA-1', 'QA-GEN-MBNAM-IN51I-RCA-1']</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -13484,10 +13632,14 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Ali Al Qaradaghi</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr"/>
+          <t>Prince Jassim Bin Hamad Of Qatar</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Hamad Bin Khalifa Al Thani</t>
+        </is>
+      </c>
       <c r="D77" t="inlineStr">
         <is>
           <t>Male</t>
@@ -13495,12 +13647,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Influential Sunni Scholar Of Islam</t>
+          <t>Qatari Royal</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Qaradagh</t>
+          <t>Doha</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -13513,7 +13665,7 @@
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
-          <t>{"Educated At": "Al-Azhar University", "Reference ID": "Q6817961"}</t>
+          <t>{"Educated At": "Royal Military Academy Sandhurst", "Reference ID": "Q6161563"}</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -13538,7 +13690,7 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/3/38/Ali_al-Qaradaghi,_Dorar_Tv_-_Jun_16,_2019_(01).jpg</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/4/46/Jassim_bin_Hamad_bin_Khalifa_Al_Thani.jpg</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
@@ -13549,7 +13701,7 @@
       <c r="T77" t="inlineStr"/>
       <c r="U77" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="V77" t="n">
@@ -13570,22 +13722,22 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>['1949-01-01']</t>
+          <t>['1978-08-25']</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>['Iraq', 'Qatar']</t>
+          <t>['Qatar']</t>
         </is>
       </c>
       <c r="AD77" t="inlineStr">
         <is>
-          <t>['Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name']</t>
+          <t>['Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name']</t>
         </is>
       </c>
       <c r="AE77" t="inlineStr">
         <is>
-          <t>['Ali Al Qaradaghi', 'علي القرة داغي', 'علي محي الدين القرة داغي', 'Әли әл Қарадағи', 'علی قرهداغی', 'עלי אל קרה דאגי', 'علي محيي الدين القرة داغي', 'على محيي الدين القره داغي', 'Ali Muhyiddin Ali Al Qaradaghi', 'عەلی قەرەداغی', 'علي محيي الدين القره داغي', 'علی محیی الدین القرہ داغی', 'Алі аль Карадагі', 'Али аль Карадаги', 'على محي الدين القرة داغي', 'Ali Qeredaxi', 'علي مُحيي الدين القره داغي']</t>
+          <t>['جاسم بن حمد آل ثاني', 'ジャーシム', 'Jasim Bin Hamad Al Thani', '賈辛·本·哈邁德·本·哈利法·阿勒薩尼', 'Jàssim ibn Hàmad ibn Khalifa Al Thani', 'Jassim Bin Hamad Bin Khalifa Al Thani', 'Jassim Bin Hamad Al Thani', "['Dzsászim bin Hamad bin Halífa ál Szání']"]</t>
         </is>
       </c>
       <c r="AF77" t="inlineStr">
@@ -13625,7 +13777,7 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Politician']</t>
         </is>
       </c>
       <c r="AN77" t="inlineStr">
@@ -13645,12 +13797,12 @@
       </c>
       <c r="AQ77" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Sibling', 'Sibling', 'Sibling', 'Sibling', 'Sibling', 'Sibling', 'Sibling', 'Sibling', 'Sibling', 'Sibling', 'Partner', 'Mother']</t>
         </is>
       </c>
       <c r="AR77" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['QA-GEN-ABHBKAT-87DYX-RCA-1', 'QA-GEN-KBHBKAT-A7NJG-RCA-1', 'QA-GEN-MBHBKAT-XHR18-RCA-1', 'QA-GEN-MBHBKAT-LRHZY-RCA-1', 'QA-GEN-MBHBKAT-C3NWO-RCA-1', 'QA-GEN-PJBHOQ-B78MR-RCA-1', 'QA-GEN-PKBHOQ-B6NQQ-RCA-1', 'QA-GEN-PAMBHOQ-3MSTL-RCA-1', 'QA-GEN-PHBHOQ-MJ0UC-RCA-1', 'QA-GEN-TBHA-K036O-RCA-1', 'QA-GEN-BBHAT-FD404-RCA-1', 'QA-GEN-MBNAM-IN51I-RCA-1']</t>
         </is>
       </c>
     </row>
@@ -13662,7 +13814,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Mohammed Saleh Al Sada</t>
+          <t>Ali Al Qaradaghi</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
@@ -13671,8 +13823,16 @@
           <t>Male</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Influential Sunni Scholar Of Islam</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Qaradagh</t>
+        </is>
+      </c>
       <c r="G78" t="n">
         <v>0</v>
       </c>
@@ -13683,7 +13843,7 @@
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr">
         <is>
-          <t>{"Educated At": "Qatar University, University of Manchester Institute of Science and Technology", "Academic Degree": "Doctor of Philosophy", "Reference ID": "Q6893312"}</t>
+          <t>{"Educated At": "Al-Azhar University", "Reference ID": "Q6817961"}</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -13708,7 +13868,7 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/3/3e/Dr._Mohammed_bin_Saleh_Al-Sada.jpg</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/3/38/Ali_al-Qaradaghi,_Dorar_Tv_-_Jun_16,_2019_(01).jpg</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
@@ -13719,7 +13879,7 @@
       <c r="T78" t="inlineStr"/>
       <c r="U78" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="V78" t="n">
@@ -13740,22 +13900,22 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['1949-01-01']</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Iraq', 'Qatar']</t>
         </is>
       </c>
       <c r="AD78" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name']</t>
+          <t>['Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name']</t>
         </is>
       </c>
       <c r="AE78" t="inlineStr">
         <is>
-          <t>['穆罕默德·薩利赫 薩達', 'モハメド・ビン・サレハ・アル＝サダ', 'Mohammed Saleh Al Sada', 'محمد صالح السادة', 'Мохаммед Салех аль Сада', '穆罕默德·萨利赫 萨达', 'محمد بن صالح السادة', 'محمد صالح السادہ']</t>
+          <t>['Ali Qeredaxi', 'علي القرة داغي', 'علي محي الدين القرة داغي', 'على محيي الدين القره داغي', 'على محي الدين القرة داغي', 'Ali Muhyiddin Ali Al Qaradaghi', 'علي محيي الدين القرة داغي', 'علي مُحيي الدين القره داغي']</t>
         </is>
       </c>
       <c r="AF78" t="inlineStr">
@@ -13795,7 +13955,7 @@
       </c>
       <c r="AM78" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Politician', 'University Teacher']</t>
         </is>
       </c>
       <c r="AN78" t="inlineStr">
@@ -13832,25 +13992,21 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Sheikha Yousuf Hasan Al Jufairi</t>
+          <t>Mohammed Saleh Al Sada</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Politician</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
+          <t>Qatari Politician</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
         <v>0</v>
       </c>
@@ -13861,7 +14017,7 @@
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr">
         <is>
-          <t>{"Reference ID": "Q7492979"}</t>
+          <t>{"Educated At": "Qatar University, University of Manchester Institute of Science and Technology", "Academic Degree": "Doctor of Philosophy", "Reference ID": "Q6893312"}</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -13884,7 +14040,11 @@
           <t>Individual</t>
         </is>
       </c>
-      <c r="R79" t="inlineStr"/>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>https://upload.wikimedia.org/wikipedia/commons/3/3e/Dr._Mohammed_bin_Saleh_Al-Sada.jpg</t>
+        </is>
+      </c>
       <c r="S79" t="inlineStr">
         <is>
           <t>qa_gen</t>
@@ -13893,7 +14053,7 @@
       <c r="T79" t="inlineStr"/>
       <c r="U79" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="V79" t="n">
@@ -13914,7 +14074,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>['1962-01-01']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
@@ -13924,12 +14084,12 @@
       </c>
       <c r="AD79" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name']</t>
+          <t>['Also Known As']</t>
         </is>
       </c>
       <c r="AE79" t="inlineStr">
         <is>
-          <t>["שייח'ה יוסוף חסן אל ג'ופאירי", 'ஷெய்கா யூசுப் ஹசன் அல் ஜுஃபைரி', 'شيخة بنت يوسف الجفيرى', 'Sheikha Yousuf Hasan Al Jufairi', 'شيخة بنت يوسف الجفيري']</t>
+          <t>['Mohammed Saleh Al Sada']</t>
         </is>
       </c>
       <c r="AF79" t="inlineStr">
@@ -13969,22 +14129,22 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Politician']</t>
         </is>
       </c>
       <c r="AN79" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Minister Of Industry And Energy', 'President Of Opec']</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['2011-01-18', '2015-12-07']</t>
         </is>
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['2018-01-01', None]</t>
         </is>
       </c>
       <c r="AQ79" t="inlineStr">
@@ -14006,23 +14166,23 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Khalid Bin Khalifa Bin Abdul Aziz Al Thani</t>
+          <t>Sheikha Yousuf Hasan Al Jufairi</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Qatari Politician</t>
+          <t>Politician</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Doha</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -14035,7 +14195,7 @@
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t>{"Academic Degree": "bachelors degree", "Reference ID": "Q83849153"}</t>
+          <t>{"Reference ID": "Q7492979"}</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -14058,11 +14218,7 @@
           <t>Individual</t>
         </is>
       </c>
-      <c r="R80" t="inlineStr">
-        <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/a/a2/Steven_Mnuchin_and_Qatari_PM_Sheikh_Khalid_Feb_2020_(cropped).jpg</t>
-        </is>
-      </c>
+      <c r="R80" t="inlineStr"/>
       <c r="S80" t="inlineStr">
         <is>
           <t>qa_gen</t>
@@ -14071,7 +14227,7 @@
       <c r="T80" t="inlineStr"/>
       <c r="U80" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="V80" t="n">
@@ -14092,7 +14248,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>['1968-01-01']</t>
+          <t>['1962-01-01']</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
@@ -14102,12 +14258,12 @@
       </c>
       <c r="AD80" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name', 'Also Known As', 'Also Known As']</t>
+          <t>['Also Known As']</t>
         </is>
       </c>
       <c r="AE80" t="inlineStr">
         <is>
-          <t>['Халид бин Халифа Әл Тани', 'خالد بن خلیفه بن عبدالعزیز آل ثانی', '哈立德·本·哈利法·本·阿蔔杜勒·阿齊茲·阿勒萨尼', 'خالد بن خليفه بن عبد العزيز آل تانى', "ח'אלד בן ח'ליפה בן עבד אל עזיז אאל ת'אני", 'Chalid Ibn Chalifa Ibn Abdulaziz Al Sani', 'Холид бин Халифа бин Абдулазиз Оли Танӣ', 'Khaled Ben Khalifa Al Thani', 'Khalid Bin Khalifa Bin Abdul Aziz Al Thani', 'Խալետ Պըն Խալիֆա Պըն Ապտուլ Ազիզ Ալ Թահանի', 'Khalid Bin Khalifa Al Thani', 'Халід бен Халіфа бен Абдул Азіз Аль Тані', 'ハーリド・ビン・ハリーファ・ビン・アブドゥルアズィーズ・アール＝サーニー', 'خالد بن خليفة بن عبد العزيز آل ثاني', "Khālid ibn Khalīfah ibn 'Abd al 'Azīz Āl Thānī", 'Χαλίντ μπιν Χαλίφα μπιν Αμπντούλ Αζίζ Αλ Θανί', 'Халид ибн Халифа ибн Абдул Азиз ел Тани', 'খালিদ বিন খলিফা বিন আব্দুল আজিজ আল থানি', 'Khalid Bin Khalifa Abdulaziz Thani', 'Halid bin Halife bin Abdülaziz es Sani', 'ハリド・ビン・ハリーファ・ビン・アブドゥル・アジズ・アール＝サーニー', '阿卜杜拉·本·哈里发·本·阿卜杜勒阿齐兹·阿勒萨尼', 'خالد بن خلیفہ الثانی', 'Халид бин Халифа бин Абдул Азиз Аль Тани', 'Khaled Ben Khalifa Ben Abdelaziz Al Thani', 'Chalid Bin Chalifa Bin Abdulasis Al Thani', '哈立德·本·哈利法·本·阿蔔杜勒·阿齊茲·阿勒薩尼', 'Chalid Ibn Chalifa Ibn Abd Al Aziz Al Sani', 'Khalid Ibn Khalifa Ibn Abdul Aziz Al Thani']</t>
+          <t>['Sheikha Yousuf Hasan Al Jufairi']</t>
         </is>
       </c>
       <c r="AF80" t="inlineStr">
@@ -14147,22 +14303,22 @@
       </c>
       <c r="AM80" t="inlineStr">
         <is>
-          <t>['Business Theorist', 'Politician']</t>
+          <t>['Politician']</t>
         </is>
       </c>
       <c r="AN80" t="inlineStr">
         <is>
-          <t>['Minister Of The Interior', 'Prime Minister Of Qatar']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
-          <t>['2020-01-28', '2020-01-28']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>['2023-03-07', '2023-03-07']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AQ80" t="inlineStr">
@@ -14184,14 +14340,10 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Ahmed Abdulla Kh H Al Thani</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Abdullah Bin Khalid Al Thani</t>
-        </is>
-      </c>
+          <t>Khalid Bin Khalifa Bin Abdul Aziz Al Thani</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
           <t>Male</t>
@@ -14199,12 +14351,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Qatari Royal</t>
+          <t>Qatari Politician</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ar Rayyan</t>
+          <t>Doha</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -14217,7 +14369,7 @@
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>{"Educated At": "London School of Economics and Political Science", "Reference ID": "Q94312498"}</t>
+          <t>{"Academic Degree": "bachelors degree", "Reference ID": "Q83849153"}</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -14242,7 +14394,7 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/7/7b/Ahmed_Abdulla_Thani.jpg</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/a/a2/Steven_Mnuchin_and_Qatari_PM_Sheikh_Khalid_Feb_2020_(cropped).jpg</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
@@ -14253,7 +14405,7 @@
       <c r="T81" t="inlineStr"/>
       <c r="U81" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="V81" t="n">
@@ -14274,7 +14426,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>['1988-08-31']</t>
+          <t>['1968-01-01']</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
@@ -14284,12 +14436,12 @@
       </c>
       <c r="AD81" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Original Script Name', 'Also Known As', 'Also Known As']</t>
+          <t>['Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Also Known As', 'Also Known As']</t>
         </is>
       </c>
       <c r="AE81" t="inlineStr">
         <is>
-          <t>['الشيخ احمد بن عبدالله بن خالد بن حمد آل ثاني', 'احمد بن عبدالله بن خالد بن حمد آل ثاني', 'Ahmed Abdulla Kh H Al Thani', 'Sheikh Ahmed Abdulla Khaled Hamad Al Thani']</t>
+          <t>['خالد بن خليفة بن عبد العزيز آل ثاني', 'Khalid Bin Khalifa Al Thani', 'Chalid Ibn Chalifa Ibn Abd Al Aziz Al Sani', '阿卜杜拉·本·哈里发·本·阿卜杜勒阿齐兹·阿勒萨尼', 'Khaled Ben Khalifa Al Thani', 'ハーリド・ビン・ハリーファ・ビン・アブドゥルアズィーズ・アール＝サーニー', 'Chalid Bin Chalifa Bin Abdulasis Al Thani', 'Khalid Bin Khalifa Abdulaziz Thani']</t>
         </is>
       </c>
       <c r="AF81" t="inlineStr">
@@ -14329,22 +14481,22 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Business Theorist', 'Politician']</t>
         </is>
       </c>
       <c r="AN81" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Minister Of The Interior', 'Prime Minister Of Qatar']</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['2020-01-28', '2020-01-28']</t>
         </is>
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['2023-03-07', '2023-03-07']</t>
         </is>
       </c>
       <c r="AQ81" t="inlineStr">
@@ -14366,19 +14518,27 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Lolwah Al Khater</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr"/>
+          <t>Ahmed Abdulla Kh H Al Thani</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Abdullah Bin Khalid Al Thani</t>
+        </is>
+      </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr"/>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Qatari Royal</t>
+        </is>
+      </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Doha</t>
+          <t>Ar Rayyan</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -14391,7 +14551,7 @@
       <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
-          <t>{"Educated At": "Hamad Bin Khalifa University, Imperial College London", "Reference ID": "Q94579585"}</t>
+          <t>{"Educated At": "London School of Economics and Political Science", "Reference ID": "Q94312498"}</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -14416,7 +14576,7 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/b/bb/Lolwah_Al-Khater_(53486244046)_(cropped).jpg</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/7/7b/Ahmed_Abdulla_Thani.jpg</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
@@ -14427,7 +14587,7 @@
       <c r="T82" t="inlineStr"/>
       <c r="U82" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="V82" t="n">
@@ -14448,22 +14608,22 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['1988-08-31']</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Qatar']</t>
         </is>
       </c>
       <c r="AD82" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name']</t>
+          <t>['Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name']</t>
         </is>
       </c>
       <c r="AE82" t="inlineStr">
         <is>
-          <t>['Лолва Рашид Мохаммед Аль Хатер', 'لولوة الخاطر', 'Lolwah Al Khater', 'லுஉலுவா அல் காத்திர்', 'لولوہ الخاطر', 'لولوه الخاطر', "לולווה אלח'אטר", '洛尔瓦·哈特']</t>
+          <t>['الشيخ احمد بن عبدالله بن خالد بن حمد آل ثاني', 'Sheikh Ahmed Abdulla Khaled Hamad Al Thani', 'Ahmed Abdulla Kh H Al Thani', 'احمد بن عبدالله بن خالد بن حمد آل ثاني']</t>
         </is>
       </c>
       <c r="AF82" t="inlineStr">
@@ -14503,7 +14663,7 @@
       </c>
       <c r="AM82" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Businessperson', 'Rider']</t>
         </is>
       </c>
       <c r="AN82" t="inlineStr">
@@ -14535,18 +14695,30 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>QA-GEN-ABAAM-NCNR8-RCA-1</t>
+          <t>QA-GEN-I-82</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Ahmad bin Abdullah Al Mahmoud</t>
+          <t>Lolwah Al Khater</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
-      <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Qatari Diplomat And Politician</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Doha</t>
+        </is>
+      </c>
       <c r="G83" t="n">
         <v>0</v>
       </c>
@@ -14557,7 +14729,7 @@
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"Educated At": "Hamad Bin Khalifa University, Imperial College London", "Reference ID": "Q94579585"}</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -14572,7 +14744,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Relative Close Associate</t>
+          <t>Politically Exposed Person</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
@@ -14580,7 +14752,11 @@
           <t>Individual</t>
         </is>
       </c>
-      <c r="R83" t="inlineStr"/>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>https://upload.wikimedia.org/wikipedia/commons/b/bb/Lolwah_Al-Khater_(53486244046)_(cropped).jpg</t>
+        </is>
+      </c>
       <c r="S83" t="inlineStr">
         <is>
           <t>qa_gen</t>
@@ -14589,7 +14765,7 @@
       <c r="T83" t="inlineStr"/>
       <c r="U83" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="V83" t="n">
@@ -14615,17 +14791,17 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Qatar']</t>
         </is>
       </c>
       <c r="AD83" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Also Known As', 'Also Known As', 'Original Script Name', 'Also Known As', 'Also Known As']</t>
         </is>
       </c>
       <c r="AE83" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Lulwa Al Khater', 'Lolwa Al Khater', 'Аль Хатер Лолва Рашид Мохаммед', 'Lolwah Rashid Mohammed Al Khater', 'Lolwah Al Khater']</t>
         </is>
       </c>
       <c r="AF83" t="inlineStr">
@@ -14665,22 +14841,22 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Diplomat', 'Politician', 'Writer']</t>
         </is>
       </c>
       <c r="AN83" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Spokesperson For The Ministry Of Foreign Affairs Of Qatar']</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['2017-01-01']</t>
         </is>
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['2022-02-01']</t>
         </is>
       </c>
       <c r="AQ83" t="inlineStr">
@@ -14697,12 +14873,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>QA-GEN-HBKAT-0TKTJ-RCA-1</t>
+          <t>QA-GEN-AMAASAH-SVQ9K-RCA-1</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Hamad bin Khalifa Al Thani</t>
+          <t>Abdulhadi Mana Abdulhadi Al Shawani Al Hajri</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
@@ -14859,12 +15035,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>QA-GEN-ABHBKAT-87DYX-RCA-1</t>
+          <t>QA-GEN-AABMAH-1KXBS-RCA-1</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Abdullah bin Hamad bin Khalifa Al Thani</t>
+          <t>Al Anoud bint Mana Al Hajri</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
@@ -15021,12 +15197,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>QA-GEN-KBHBKAT-A7NJG-RCA-1</t>
+          <t>QA-GEN-EAM-L9PZJ-RCA-1</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Khalifa bin Hamad bin Khalifa Al Thani</t>
+          <t>Eissa Al Mana</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
@@ -15183,12 +15359,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>QA-GEN-MBHBKAT-XHR18-RCA-1</t>
+          <t>QA-GEN-AAKHAT-U7E8Q-RCA-1</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Maha bint Hamad bin Khalifa Al Thani</t>
+          <t>Ahmed Abdulla KH H Al Thani</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
@@ -15345,12 +15521,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>QA-GEN-MBHBKAT-LRHZY-RCA-1</t>
+          <t>QA-GEN-ABHBKAT-87DYX-RCA-1</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Mishaal bin Hamad bin Khalifa Al Thani</t>
+          <t>Abdullah bin Hamad bin Khalifa Al Thani</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
@@ -15507,12 +15683,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>QA-GEN-MBHBKAT-C3NWO-RCA-1</t>
+          <t>QA-GEN-KBHAT-OL3FU-RCA-1</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Mohammed bin Hamad bin Khalifa Al Thani</t>
+          <t>Khalid bin Hamad Al Thani</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
@@ -15669,12 +15845,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>QA-GEN-PJBHOQ-PNKIK-RCA-1</t>
+          <t>QA-GEN-MBHBKAT-XHR18-RCA-1</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Prince Jassim bin Hamad of Qatar</t>
+          <t>Maha bint Hamad bin Khalifa Al Thani</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
@@ -15831,12 +16007,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>QA-GEN-PJBHOQ-B78MR-RCA-1</t>
+          <t>QA-GEN-MBHBKAT-LRHZY-RCA-1</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Prince Joaan bin Hamad of Qatar</t>
+          <t>Mishaal bin Hamad bin Khalifa Al Thani</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
@@ -15993,12 +16169,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>QA-GEN-PKBHOQ-B6NQQ-RCA-1</t>
+          <t>QA-GEN-MBHBKAT-C3NWO-RCA-1</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Prince Khalifa bin Hamad of Qatar</t>
+          <t>Mohammed bin Hamad bin Khalifa Al Thani</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
@@ -16155,12 +16331,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>QA-GEN-PAMBHOQ-3MSTL-RCA-1</t>
+          <t>QA-GEN-PJBHOQ-PNKIK-RCA-1</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Princess Al Mayassa bint Hamad of Qatar</t>
+          <t>Prince Jassim bin Hamad of Qatar</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
@@ -16317,12 +16493,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>QA-GEN-PHBHOQ-MJ0UC-RCA-1</t>
+          <t>QA-GEN-PJBHOQ-B78MR-RCA-1</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Princess Hind bint Hamad of Qatar</t>
+          <t>Prince Joaan bin Hamad of Qatar</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
@@ -16479,12 +16655,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>QA-GEN-TBHAT-28KU2-RCA-1</t>
+          <t>QA-GEN-PKBHOQ-B6NQQ-RCA-1</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Thani bin Hamad Al Thani</t>
+          <t>Prince Khalifa bin Hamad of Qatar</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
@@ -16641,12 +16817,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>QA-GEN-TBHA-K036O-RCA-1</t>
+          <t>QA-GEN-PAMBHOQ-3MSTL-RCA-1</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Tamim bin Hamad Al</t>
+          <t>Princess Al Mayassa bint Hamad of Qatar</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
@@ -16803,12 +16979,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>QA-GEN-ABKAT-KXNJ5-RCA-1</t>
+          <t>QA-GEN-PHBHOQ-MJ0UC-RCA-1</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Abdelaziz bin Khalifa Al Thani</t>
+          <t>Princess Hind bint Hamad of Qatar</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
@@ -16965,12 +17141,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>QA-GEN-ABKAT-7QHEU-RCA-1</t>
+          <t>QA-GEN-TBHA-K036O-RCA-1</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Abdullah bin Khalifa Al Thani</t>
+          <t>Tamim bin Hamad Al</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
@@ -17127,12 +17303,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>QA-GEN-MBKAT-TDAMF-RCA-1</t>
+          <t>QA-GEN-TBHAT-28KU2-RCA-1</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Mohammed bin Khalifa Al Thani</t>
+          <t>Thani bin Hamad Al Thani</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
@@ -17289,12 +17465,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>QA-GEN-AABMAH-1KXBS-RCA-1</t>
+          <t>QA-GEN-ABAAM-NCNR8-RCA-1</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Al Anoud bint Mana Al Hajri</t>
+          <t>Ahmad bin Abdullah Al Mahmoud</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
@@ -17451,12 +17627,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>QA-GEN-JBHAT-EB0Z0-RCA-1</t>
+          <t>QA-GEN-HBKAT-0TKTJ-RCA-1</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Jawaher bint Hamad Al Thani</t>
+          <t>Hamad bin Khalifa Al Thani</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
@@ -17613,12 +17789,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>QA-GEN-NBHAD-JGB3R-RCA-1</t>
+          <t>QA-GEN-KBHBKAT-A7NJG-RCA-1</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Noora bint Hathal Al Dosari</t>
+          <t>Khalifa bin Hamad bin Khalifa Al Thani</t>
         </is>
       </c>
       <c r="C102" t="inlineStr"/>
@@ -17775,12 +17951,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>QA-GEN-JJ-OM38T-RCA-1</t>
+          <t>QA-GEN-ABKAT-KXNJ5-RCA-1</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Janet Jackson</t>
+          <t>Abdelaziz bin Khalifa Al Thani</t>
         </is>
       </c>
       <c r="C103" t="inlineStr"/>
@@ -17937,12 +18113,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>QA-GEN-LBJBH-RUAHV-RCA-1</t>
+          <t>QA-GEN-ABKAT-7QHEU-RCA-1</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Lolwa bint Jassim bin Hamad</t>
+          <t>Abdullah bin Khalifa Al Thani</t>
         </is>
       </c>
       <c r="C104" t="inlineStr"/>
@@ -18099,12 +18275,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>QA-GEN-MBNAM-IN51I-RCA-1</t>
+          <t>QA-GEN-MBKAT-4O4S5-RCA-1</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Moza bint Nasser Al Missned</t>
+          <t>Mohammed bin Khalifa Al Thani</t>
         </is>
       </c>
       <c r="C105" t="inlineStr"/>
@@ -18261,12 +18437,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>QA-GEN-BBHAT-FD404-RCA-1</t>
+          <t>QA-GEN-HBSAT-LEUBZ-RCA-1</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Buthaina bint Hamad Al Thani</t>
+          <t>Hamad bin Suhaim Al Thani</t>
         </is>
       </c>
       <c r="C106" t="inlineStr"/>
@@ -18423,12 +18599,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>QA-GEN-HBSAT-LEUBZ-RCA-1</t>
+          <t>QA-GEN-KBHAT-ND19D-RCA-1</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Hamad bin Suhaim Al Thani</t>
+          <t>Khalifa bin Hamad Al Thani</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
@@ -18585,12 +18761,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>QA-GEN-KBHAT-ND19D-RCA-1</t>
+          <t>QA-GEN-HBJBJAT-W665T-RCA-1</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Khalifa bin Hamad Al Thani</t>
+          <t>Hamad bin Jassim bin Jaber Al Thani</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
@@ -18747,12 +18923,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>QA-GEN-HBJBJAT-W665T-RCA-1</t>
+          <t>QA-GEN-HBKBAAT-ZM37Z-RCA-1</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Hamad bin Jassim bin Jaber Al Thani</t>
+          <t>Hamad Bin Khalifa Bin Ahmed Al Thani</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
@@ -18909,12 +19085,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>QA-GEN-HBKBAAT-ZM37Z-RCA-1</t>
+          <t>QA-GEN-SBHAT-GX4H3-RCA-1</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Hamad Bin Khalifa Bin Ahmed Al Thani</t>
+          <t>Suhaim bin Hamad Al Thani</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
@@ -19071,12 +19247,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>QA-GEN-SBHAT-GX4H3-RCA-1</t>
+          <t>QA-GEN-JBHAT-EB0Z0-RCA-1</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Suhaim bin Hamad Al Thani</t>
+          <t>Jawaher bint Hamad Al Thani</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
@@ -19233,12 +19409,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>QA-GEN-AMAASAH-SVQ9K-RCA-1</t>
+          <t>QA-GEN-NBHAD-JGB3R-RCA-1</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Abdulhadi Mana Abdulhadi Al Shawani Al Hajri</t>
+          <t>Noora bint Hathal Al Dosari</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
@@ -19395,12 +19571,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>QA-GEN-EAM-L9PZJ-RCA-1</t>
+          <t>QA-GEN-JJ-OM38T-RCA-1</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Eissa Al Mana</t>
+          <t>Janet Jackson</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
@@ -19557,12 +19733,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>QA-GEN-AAKHAT-U7E8Q-RCA-1</t>
+          <t>QA-GEN-LBJBH-RUAHV-RCA-1</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Ahmed Abdulla KH H Al Thani</t>
+          <t>Lolwa bint Jassim bin Hamad</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
@@ -19719,12 +19895,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>QA-GEN-KBHAT-OL3FU-RCA-1</t>
+          <t>QA-GEN-MBNAM-IN51I-RCA-1</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Khalid bin Hamad Al Thani</t>
+          <t>Moza bint Nasser Al Missned</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
@@ -19878,6 +20054,168 @@
         </is>
       </c>
     </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>QA-GEN-BBHAT-FD404-RCA-1</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Buthaina bint Hamad Al Thani</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr"/>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="n">
+        <v>0</v>
+      </c>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>Idenfo</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>General Qatar</t>
+        </is>
+      </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Relative Close Associate</t>
+        </is>
+      </c>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>Individual</t>
+        </is>
+      </c>
+      <c r="R116" t="inlineStr"/>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>qa_gen</t>
+        </is>
+      </c>
+      <c r="T116" t="inlineStr"/>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>2025-12-24</t>
+        </is>
+      </c>
+      <c r="V116" t="n">
+        <v>1</v>
+      </c>
+      <c r="W116" t="inlineStr"/>
+      <c r="X116" t="inlineStr"/>
+      <c r="Y116" t="inlineStr"/>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD116" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE116" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF116" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG116" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AH116" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI116" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ116" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK116" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL116" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AM116" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AN116" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AO116" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AP116" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AQ116" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AR116" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
